--- a/EndoPredict_Selenium_Test_Report.xlsx
+++ b/EndoPredict_Selenium_Test_Report.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Detailed Test Cases (124)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Detailed Test Cases (222)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="67" customWidth="1" min="1" max="1"/>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>124</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5"/>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>124</v>
+        <v>222</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>413.52 sec</t>
+          <t>595.87 sec</t>
         </is>
       </c>
     </row>
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>0</v>
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>0</v>
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>0</v>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>0</v>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>0</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D19" s="7" t="n">
         <v>0</v>
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>0</v>
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>0</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>0</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>0</v>
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>0</v>
@@ -894,15 +894,57 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -922,12 +964,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:I223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -1015,11 +1057,11 @@
         </is>
       </c>
       <c r="G2" s="9" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>15:30:55</t>
+          <t>19:39:09</t>
         </is>
       </c>
       <c r="I2" s="10" t="inlineStr"/>
@@ -1056,11 +1098,11 @@
         </is>
       </c>
       <c r="G3" s="9" t="n">
-        <v>0.662</v>
+        <v>0.659</v>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>15:30:55</t>
+          <t>19:39:09</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr"/>
@@ -1097,11 +1139,11 @@
         </is>
       </c>
       <c r="G4" s="9" t="n">
-        <v>0.663</v>
+        <v>0.664</v>
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>15:30:56</t>
+          <t>19:39:10</t>
         </is>
       </c>
       <c r="I4" s="10" t="inlineStr"/>
@@ -1138,11 +1180,11 @@
         </is>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.659</v>
+        <v>0.663</v>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>15:30:57</t>
+          <t>19:39:11</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr"/>
@@ -1179,11 +1221,11 @@
         </is>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.654</v>
+        <v>0.674</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>15:30:57</t>
+          <t>19:39:11</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
@@ -1220,11 +1262,11 @@
         </is>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.662</v>
+        <v>0.66</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>15:30:58</t>
+          <t>19:39:12</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr"/>
@@ -1261,11 +1303,11 @@
         </is>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.667</v>
+        <v>0.67</v>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>15:30:59</t>
+          <t>19:39:13</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr"/>
@@ -1302,11 +1344,11 @@
         </is>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.652</v>
+        <v>0.653</v>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>15:30:59</t>
+          <t>19:39:13</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr"/>
@@ -1343,11 +1385,11 @@
         </is>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>15:31:00</t>
+          <t>19:39:14</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
@@ -1384,11 +1426,11 @@
         </is>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.675</v>
+        <v>0.667</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>15:31:01</t>
+          <t>19:39:15</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr"/>
@@ -1425,11 +1467,11 @@
         </is>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>15:31:01</t>
+          <t>19:39:15</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr"/>
@@ -1466,11 +1508,11 @@
         </is>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.657</v>
+        <v>0.654</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>15:31:01</t>
+          <t>19:39:15</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr"/>
@@ -1478,22 +1520,22 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>DASH-001</t>
+          <t>NAV-013</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Verify Total Patients Stat Card</t>
+          <t>Brand Logo Click Navigation</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Ensure Total Patients metric card is displayed</t>
+          <t>Click top logo banner to navigate to home view</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1507,11 +1549,11 @@
         </is>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>15:31:03</t>
+          <t>19:39:16</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr"/>
@@ -1519,22 +1561,22 @@
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>DASH-002</t>
+          <t>NAV-014</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Verify High Risk Cases Stat Card</t>
+          <t>Route State Persistence Check</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Ensure High Risk / Emergency cases stat is rendered</t>
+          <t>Ensure active tab remains unchanged during background operations</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -1548,11 +1590,11 @@
         </is>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>15:31:03</t>
+          <t>19:39:16</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr"/>
@@ -1560,22 +1602,22 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>DASH-003</t>
+          <t>NAV-015</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Verify Treatments Completed Stat Card</t>
+          <t>Keyboard Tab Traversal</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Check Treatments Completed stat metric on Dashboard</t>
+          <t>Verify interactive buttons respond to keyboard navigation</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1589,11 +1631,11 @@
         </is>
       </c>
       <c r="G16" s="9" t="n">
-        <v>6.074</v>
+        <v>0.006</v>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>15:31:03</t>
+          <t>19:39:16</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr"/>
@@ -1601,7 +1643,7 @@
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>DASH-004</t>
+          <t>DASH-001</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -1611,12 +1653,12 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Verify Pending Follow-ups Stat Card</t>
+          <t>Verify Total Patients Stat Card</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Check Pending Follow-ups metric card display</t>
+          <t>Ensure Total Patients metric card is displayed</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -1630,11 +1672,11 @@
         </is>
       </c>
       <c r="G17" s="9" t="n">
-        <v>3.045</v>
+        <v>0.008</v>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>15:31:09</t>
+          <t>19:39:17</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr"/>
@@ -1642,7 +1684,7 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>DASH-005</t>
+          <t>DASH-002</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -1652,12 +1694,12 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Verify Recent Patients Table / List</t>
+          <t>Verify High Risk Cases Stat Card</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Verify Recent Patients list container exists on Dashboard</t>
+          <t>Ensure High Risk / Emergency cases stat is rendered</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -1675,7 +1717,7 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>15:31:12</t>
+          <t>19:39:17</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr"/>
@@ -1683,7 +1725,7 @@
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>DASH-006</t>
+          <t>DASH-003</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -1693,12 +1735,12 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Verify Upcoming Appointments Summary</t>
+          <t>Verify Treatments Completed Stat Card</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Ensure upcoming appointments panel is rendered</t>
+          <t>Check Treatments Completed stat metric on Dashboard</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -1712,11 +1754,11 @@
         </is>
       </c>
       <c r="G19" s="9" t="n">
-        <v>3.058</v>
+        <v>6.077</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>15:31:12</t>
+          <t>19:39:17</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr"/>
@@ -1724,7 +1766,7 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>DASH-007</t>
+          <t>DASH-004</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -1734,12 +1776,12 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Quick Action: Add Patient Button</t>
+          <t>Verify Pending Follow-ups Stat Card</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Verify Quick Action button navigating to Add Patient</t>
+          <t>Check Pending Follow-ups metric card display</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -1753,11 +1795,11 @@
         </is>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.441</v>
+        <v>3.042</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>15:31:15</t>
+          <t>19:39:23</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr"/>
@@ -1765,7 +1807,7 @@
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>DASH-008</t>
+          <t>DASH-005</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -1775,12 +1817,12 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Quick Action: AI Risk Calculation</t>
+          <t>Verify Practice Revenue Stat Metric</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Verify Quick Action button navigating to AI Risk Assessment</t>
+          <t>Ensure revenue and clinical volume stats display</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -1794,11 +1836,11 @@
         </is>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.879</v>
+        <v>6.014</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>15:31:16</t>
+          <t>19:39:26</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr"/>
@@ -1806,7 +1848,7 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>DASH-009</t>
+          <t>DASH-006</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -1816,12 +1858,12 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Dashboard Visual Cards Rendering</t>
+          <t>Verify Recent Patients Table / List</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Verify dashboard visual elements render properly</t>
+          <t>Verify Recent Patients list container exists on Dashboard</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -1835,11 +1877,11 @@
         </is>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>15:31:16</t>
+          <t>19:39:32</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr"/>
@@ -1847,7 +1889,7 @@
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>DASH-010</t>
+          <t>DASH-007</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -1857,12 +1899,12 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>System Header &amp; Practice Name Banner</t>
+          <t>Verify Recent Patient Row Preview Click</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Verify EndoPredict brand title and doctor welcome banner</t>
+          <t>Test patient row interaction from Dashboard list</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -1876,11 +1918,11 @@
         </is>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>15:31:16</t>
+          <t>19:39:32</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr"/>
@@ -1888,22 +1930,22 @@
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>MAP-001</t>
+          <t>DASH-008</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Dental Map</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>32 Adult Teeth Visualization Render</t>
+          <t>Verify Upcoming Appointments Summary</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Verify interactive tooth map displays teeth grid</t>
+          <t>Ensure upcoming appointments panel is rendered</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -1917,11 +1959,11 @@
         </is>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.011</v>
+        <v>3.059</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>15:31:17</t>
+          <t>19:39:32</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr"/>
@@ -1929,22 +1971,22 @@
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>MAP-002</t>
+          <t>DASH-009</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Dental Map</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Select Upper Arch Tooth (e.g., Tooth 14/16)</t>
+          <t>Quick Action: Add Patient Button</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Click SVG tooth node 14 or 16 on upper arch</t>
+          <t>Verify Quick Action button navigating to Add Patient</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -1958,11 +2000,11 @@
         </is>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.172</v>
+        <v>0.444</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>15:31:17</t>
+          <t>19:39:35</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr"/>
@@ -1970,22 +2012,22 @@
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>MAP-003</t>
+          <t>DASH-010</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Dental Map</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Select Lower Arch Tooth (e.g., Tooth 36/46)</t>
+          <t>Quick Action: AI Risk Calculation</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Click SVG tooth node 36 or 46 on lower arch</t>
+          <t>Verify Quick Action button navigating to AI Risk Assessment</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -1999,11 +2041,11 @@
         </is>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.093</v>
+        <v>0.889</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>15:31:17</t>
+          <t>19:39:35</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr"/>
@@ -2011,22 +2053,22 @@
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>MAP-004</t>
+          <t>DASH-011</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Dental Map</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Verify Tooth Details Panel Opening</t>
+          <t>Quick Action: Open Calendar Schedule</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Ensure tooth details drawer opens upon tooth selection</t>
+          <t>Verify Quick Action button for Appointments schedule</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -2040,11 +2082,11 @@
         </is>
       </c>
       <c r="G27" s="9" t="n">
-        <v>6.08</v>
+        <v>0.464</v>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>15:31:17</t>
+          <t>19:39:36</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr"/>
@@ -2052,22 +2094,22 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>MAP-005</t>
+          <t>DASH-012</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Dental Map</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Toggle FDI Numbering System</t>
+          <t>Dashboard Visual Cards Rendering</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Switch numbering notation system to FDI standard</t>
+          <t>Verify dashboard visual elements render properly</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -2081,11 +2123,11 @@
         </is>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>15:31:24</t>
+          <t>19:39:37</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr"/>
@@ -2093,22 +2135,22 @@
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>MAP-006</t>
+          <t>DASH-013</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Dental Map</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Toggle Universal Numbering System</t>
+          <t>System Header &amp; Practice Title Banner</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Switch numbering notation system to Universal (1-32)</t>
+          <t>Verify EndoPredict brand title and doctor welcome banner</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -2122,11 +2164,11 @@
         </is>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>15:31:24</t>
+          <t>19:39:37</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr"/>
@@ -2134,22 +2176,22 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>MAP-007</t>
+          <t>DASH-014</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Dental Map</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Toggle Palmer Numbering System</t>
+          <t>Clinical Alert Notice Banner</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Switch numbering notation system to Palmer notation</t>
+          <t>Check high-priority clinical notification banner</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -2163,11 +2205,11 @@
         </is>
       </c>
       <c r="G30" s="9" t="n">
-        <v>3.043</v>
+        <v>0.007</v>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>15:31:24</t>
+          <t>19:39:37</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr"/>
@@ -2175,22 +2217,22 @@
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>MAP-008</t>
+          <t>DASH-015</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Dental Map</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Filter Teeth by Status: All</t>
+          <t>Summary Metrics Refresh Indicator</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Select 'All' teeth filter option</t>
+          <t>Verify realtime dashboard data refresh state</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -2204,11 +2246,11 @@
         </is>
       </c>
       <c r="G31" s="9" t="n">
-        <v>3.018</v>
+        <v>0.003</v>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>15:31:27</t>
+          <t>19:39:37</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr"/>
@@ -2216,7 +2258,7 @@
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>MAP-009</t>
+          <t>MAP-001</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
@@ -2226,12 +2268,12 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Filter Teeth by Status: Healthy</t>
+          <t>32 Adult Teeth Visualization Render</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>Filter teeth showing Healthy status</t>
+          <t>Verify interactive tooth map displays teeth grid</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2245,11 +2287,11 @@
         </is>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>15:31:30</t>
+          <t>19:39:37</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr"/>
@@ -2257,7 +2299,7 @@
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>MAP-010</t>
+          <t>MAP-002</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
@@ -2267,12 +2309,12 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Filter Teeth by Status: Emergency/Pulpitis</t>
+          <t>Select Upper Arch Tooth 14</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Filter teeth showing Emergency / Pulpitis condition</t>
+          <t>Click SVG tooth node 14 on upper right arch</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -2286,11 +2328,11 @@
         </is>
       </c>
       <c r="G33" s="9" t="n">
-        <v>6.055</v>
+        <v>0.145</v>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>15:31:30</t>
+          <t>19:39:37</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr"/>
@@ -2298,7 +2340,7 @@
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>MAP-011</t>
+          <t>MAP-003</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -2308,12 +2350,12 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Toggle Heatmap Risk Mode</t>
+          <t>Select Upper Arch Tooth 16</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Enable heat map overlay for pain and inflammation visualization</t>
+          <t>Click SVG tooth node 16 on upper molar arch</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -2327,11 +2369,11 @@
         </is>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.031</v>
+        <v>0.061</v>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>15:31:36</t>
+          <t>19:39:38</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr"/>
@@ -2339,7 +2381,7 @@
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>MAP-012</t>
+          <t>MAP-004</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
@@ -2349,12 +2391,12 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Tooth Element Hover Highlight</t>
+          <t>Select Lower Arch Tooth 36</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>Verify hover interaction over tooth element</t>
+          <t>Click SVG tooth node 36 on lower left molar arch</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -2368,11 +2410,11 @@
         </is>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.008</v>
+        <v>0.057</v>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>15:31:36</t>
+          <t>19:39:38</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr"/>
@@ -2380,7 +2422,7 @@
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>MAP-013</t>
+          <t>MAP-005</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -2390,12 +2432,12 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Tooth Diagnostic History Tab</t>
+          <t>Select Lower Arch Tooth 46</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>Check diagnostic notes for selected tooth</t>
+          <t>Click SVG tooth node 46 on lower right molar arch</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -2409,11 +2451,11 @@
         </is>
       </c>
       <c r="G36" s="9" t="n">
-        <v>3.036</v>
+        <v>0.058</v>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>15:31:36</t>
+          <t>19:39:38</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr"/>
@@ -2421,7 +2463,7 @@
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>MAP-014</t>
+          <t>MAP-006</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -2431,12 +2473,12 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Primary (Pediatric) Teeth Mode Toggle</t>
+          <t>Verify Tooth Details Panel Opening</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Check primary 20 teeth pediatric view option</t>
+          <t>Ensure tooth details drawer opens upon tooth selection</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -2450,11 +2492,11 @@
         </is>
       </c>
       <c r="G37" s="9" t="n">
-        <v>6.031</v>
+        <v>6.076</v>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>15:31:39</t>
+          <t>19:39:38</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr"/>
@@ -2462,7 +2504,7 @@
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>MAP-015</t>
+          <t>MAP-007</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
@@ -2472,12 +2514,12 @@
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Close Tooth Details Panel</t>
+          <t>Toggle FDI Numbering System</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>Dismiss tooth details panel</t>
+          <t>Switch numbering notation system to FDI standard</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -2491,11 +2533,11 @@
         </is>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.625</v>
+        <v>0.013</v>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>15:31:45</t>
+          <t>19:39:44</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr"/>
@@ -2503,22 +2545,22 @@
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>PAT-001</t>
+          <t>MAP-008</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Patient Directory</t>
+          <t>Dental Map</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Load Patients Directory Page</t>
+          <t>Toggle Universal Numbering System</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Navigate to Patients page and verify patient directory table</t>
+          <t>Switch numbering notation system to Universal (1-32)</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -2532,11 +2574,11 @@
         </is>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>15:31:46</t>
+          <t>19:39:44</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr"/>
@@ -2544,22 +2586,22 @@
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>PAT-002</t>
+          <t>MAP-009</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Patient Directory</t>
+          <t>Dental Map</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Search Patient by Name</t>
+          <t>Toggle Palmer Numbering System</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Type patient name in search box and verify filter</t>
+          <t>Switch numbering notation system to Palmer notation</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -2573,11 +2615,11 @@
         </is>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0.4</v>
+        <v>3.054</v>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>15:31:46</t>
+          <t>19:39:44</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr"/>
@@ -2585,22 +2627,22 @@
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>PAT-003</t>
+          <t>MAP-010</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Patient Directory</t>
+          <t>Dental Map</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Search Patient by Non-existent Query</t>
+          <t>Filter Teeth by Status: All</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Type non-existent search query and verify filtered state</t>
+          <t>Select 'All' teeth filter option</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -2614,11 +2656,11 @@
         </is>
       </c>
       <c r="G41" s="9" t="n">
-        <v>0.352</v>
+        <v>3.05</v>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>15:31:47</t>
+          <t>19:39:47</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr"/>
@@ -2626,22 +2668,22 @@
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>PAT-004</t>
+          <t>MAP-011</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Patient Directory</t>
+          <t>Dental Map</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Clear Patient Search Filter</t>
+          <t>Filter Teeth by Status: Healthy</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Clear search input field to reset patient list</t>
+          <t>Filter teeth showing Healthy status</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -2655,11 +2697,11 @@
         </is>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0.34</v>
+        <v>0.032</v>
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>15:31:47</t>
+          <t>19:39:50</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr"/>
@@ -2667,22 +2709,22 @@
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>PAT-005</t>
+          <t>MAP-012</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Patient Directory</t>
+          <t>Dental Map</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Open Add New Patient Modal</t>
+          <t>Filter Teeth by Status: Emergency/Pulpitis</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>Click '+ Add Patient' or 'New Patient' button</t>
+          <t>Filter teeth showing Emergency / Pulpitis condition</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -2696,11 +2738,11 @@
         </is>
       </c>
       <c r="G43" s="9" t="n">
-        <v>3.041</v>
+        <v>6.122</v>
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
-          <t>15:31:47</t>
+          <t>19:39:50</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr"/>
@@ -2708,22 +2750,22 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>PAT-006</t>
+          <t>MAP-013</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Patient Directory</t>
+          <t>Dental Map</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Add Patient Modal - Name Input</t>
+          <t>Filter Teeth by Status: Completed RCT</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>Fill patient full name in modal input</t>
+          <t>Filter teeth showing completed root canal status</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -2737,11 +2779,11 @@
         </is>
       </c>
       <c r="G44" s="9" t="n">
-        <v>0.264</v>
+        <v>0.006</v>
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
-          <t>15:31:50</t>
+          <t>19:39:56</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr"/>
@@ -2749,22 +2791,22 @@
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>PAT-007</t>
+          <t>MAP-014</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Patient Directory</t>
+          <t>Dental Map</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Add Patient Modal - Age Input</t>
+          <t>Toggle Heatmap Risk Mode</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>Input patient age in number field</t>
+          <t>Enable heat map overlay for pain and inflammation visualization</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -2778,11 +2820,11 @@
         </is>
       </c>
       <c r="G45" s="9" t="n">
-        <v>0.057</v>
+        <v>0.032</v>
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
-          <t>15:31:51</t>
+          <t>19:39:56</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr"/>
@@ -2790,22 +2832,22 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>PAT-008</t>
+          <t>MAP-015</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Patient Directory</t>
+          <t>Dental Map</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Add Patient Modal - Gender Select</t>
+          <t>Tooth Element Hover Highlight</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>Select gender option (Female/Male)</t>
+          <t>Verify hover interaction over tooth element</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -2819,11 +2861,11 @@
         </is>
       </c>
       <c r="G46" s="9" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
-          <t>15:31:51</t>
+          <t>19:39:56</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr"/>
@@ -2831,22 +2873,22 @@
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>PAT-009</t>
+          <t>MAP-016</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Patient Directory</t>
+          <t>Dental Map</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Add Patient Modal - Phone Input</t>
+          <t>Tooth Diagnostic History Tab</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>Input contact phone number</t>
+          <t>Check diagnostic notes for selected tooth</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -2860,11 +2902,11 @@
         </is>
       </c>
       <c r="G47" s="9" t="n">
-        <v>0.136</v>
+        <v>3.047</v>
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
-          <t>15:31:51</t>
+          <t>19:39:56</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr"/>
@@ -2872,22 +2914,22 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>PAT-010</t>
+          <t>MAP-017</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Patient Directory</t>
+          <t>Dental Map</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Add Patient Modal - Tooth Selection</t>
+          <t>Primary (Pediatric) Teeth Mode Toggle</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>Select tooth number dropdown/picker</t>
+          <t>Check primary 20 teeth pediatric view option</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -2901,11 +2943,11 @@
         </is>
       </c>
       <c r="G48" s="9" t="n">
-        <v>0.006</v>
+        <v>6.064</v>
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>15:31:51</t>
+          <t>19:39:59</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr"/>
@@ -2913,22 +2955,22 @@
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>PAT-011</t>
+          <t>MAP-018</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Patient Directory</t>
+          <t>Dental Map</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Add Patient Modal - Diagnosis Selection</t>
+          <t>Tooth Surface Selector (Occlusal/Mesial/Distal)</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Select diagnosis type (e.g., Irreversible Pulpitis)</t>
+          <t>Verify tooth surface anatomical location selector</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -2942,11 +2984,11 @@
         </is>
       </c>
       <c r="G49" s="9" t="n">
-        <v>0.003</v>
+        <v>6.037</v>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>15:31:51</t>
+          <t>19:40:05</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr"/>
@@ -2954,22 +2996,22 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>PAT-012</t>
+          <t>MAP-019</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Patient Directory</t>
+          <t>Dental Map</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Add Patient Modal - Pain Score Slider</t>
+          <t>Apical Radiograph Thumbnail Preview</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Set pain intensity score (0 - 10 scale)</t>
+          <t>Verify diagnostic X-ray image thumbnail display</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -2983,11 +3025,11 @@
         </is>
       </c>
       <c r="G50" s="9" t="n">
-        <v>3.036</v>
+        <v>0.01</v>
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>15:31:51</t>
+          <t>19:40:11</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr"/>
@@ -2995,22 +3037,22 @@
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>PAT-013</t>
+          <t>MAP-020</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Patient Directory</t>
+          <t>Dental Map</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Submit New Patient Form</t>
+          <t>Close Tooth Details Panel</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>Click Save / Add Patient submit button</t>
+          <t>Dismiss tooth details panel</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -3024,11 +3066,11 @@
         </is>
       </c>
       <c r="G51" s="9" t="n">
-        <v>0.014</v>
+        <v>0.623</v>
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>15:31:54</t>
+          <t>19:40:11</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr"/>
@@ -3036,7 +3078,7 @@
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>PAT-014</t>
+          <t>PAT-001</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -3046,12 +3088,12 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>View Patient Profile Details</t>
+          <t>Load Patients Directory Page</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Click existing patient row to view profile</t>
+          <t>Navigate to Patients page and verify patient directory table</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
@@ -3065,11 +3107,11 @@
         </is>
       </c>
       <c r="G52" s="9" t="n">
-        <v>3.044</v>
+        <v>0.007</v>
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>15:31:54</t>
+          <t>19:40:13</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr"/>
@@ -3077,7 +3119,7 @@
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>PAT-015</t>
+          <t>PAT-002</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -3087,12 +3129,12 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Close / Cancel Add Patient Modal</t>
+          <t>Search Patient by First Name</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>Dismiss patient modal dialog</t>
+          <t>Type patient first name in search box and verify filter</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -3106,11 +3148,11 @@
         </is>
       </c>
       <c r="G53" s="9" t="n">
-        <v>0.728</v>
+        <v>0.439</v>
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>15:31:57</t>
+          <t>19:40:13</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr"/>
@@ -3118,22 +3160,22 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>CASE-001</t>
+          <t>PAT-003</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Patient Case File</t>
+          <t>Patient Directory</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Open Patient Case File Main View</t>
+          <t>Search Patient by Last Name</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Navigate to Patient Case File module</t>
+          <t>Type patient last name in search query</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
@@ -3147,11 +3189,11 @@
         </is>
       </c>
       <c r="G54" s="9" t="n">
-        <v>3.055</v>
+        <v>0.402</v>
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
-          <t>15:31:58</t>
+          <t>19:40:13</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr"/>
@@ -3159,22 +3201,22 @@
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>CASE-002</t>
+          <t>PAT-004</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Patient Case File</t>
+          <t>Patient Directory</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Demographics Sub-Tab</t>
+          <t>Search Patient by Phone Number</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>Switch to Demographics sub-tab</t>
+          <t>Type phone number in patient directory search</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
@@ -3188,11 +3230,11 @@
         </is>
       </c>
       <c r="G55" s="9" t="n">
-        <v>3.017</v>
+        <v>0.345</v>
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
-          <t>15:32:01</t>
+          <t>19:40:14</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr"/>
@@ -3200,22 +3242,22 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>CASE-003</t>
+          <t>PAT-005</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Patient Case File</t>
+          <t>Patient Directory</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Clinical History Sub-Tab</t>
+          <t>Search Patient by Non-existent Query</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Switch to Clinical History sub-tab</t>
+          <t>Type non-existent search query and verify filtered state</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -3229,11 +3271,11 @@
         </is>
       </c>
       <c r="G56" s="9" t="n">
-        <v>0.031</v>
+        <v>0.359</v>
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>15:32:04</t>
+          <t>19:40:14</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr"/>
@@ -3241,22 +3283,22 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>CASE-004</t>
+          <t>PAT-006</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Patient Case File</t>
+          <t>Patient Directory</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Edit Medical History Notes Field</t>
+          <t>Clear Patient Search Filter</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>Verify editable medical history text area</t>
+          <t>Clear search input field to reset patient list</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
@@ -3270,11 +3312,11 @@
         </is>
       </c>
       <c r="G57" s="9" t="n">
-        <v>0.007</v>
+        <v>0.348</v>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
-          <t>15:32:04</t>
+          <t>19:40:14</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr"/>
@@ -3282,22 +3324,22 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>CASE-005</t>
+          <t>PAT-007</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Patient Case File</t>
+          <t>Patient Directory</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Edit Allergies &amp; Risk Factors Notes</t>
+          <t>Filter Patients by High Risk Level</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>Verify allergies &amp; drug hypersensitivity field</t>
+          <t>Filter directory to show High Risk cases only</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
@@ -3311,11 +3353,11 @@
         </is>
       </c>
       <c r="G58" s="9" t="n">
-        <v>6.046</v>
+        <v>6.044</v>
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>15:32:04</t>
+          <t>19:40:15</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr"/>
@@ -3323,22 +3365,22 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>CASE-006</t>
+          <t>PAT-008</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Patient Case File</t>
+          <t>Patient Directory</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Treatment Planning Sub-Tab</t>
+          <t>Sort Patients Table by Name</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>Switch to Treatment Planning sub-tab</t>
+          <t>Click table column header to sort by patient name</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -3352,11 +3394,11 @@
         </is>
       </c>
       <c r="G59" s="9" t="n">
-        <v>3.053</v>
+        <v>3.012</v>
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
-          <t>15:32:11</t>
+          <t>19:40:21</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr"/>
@@ -3364,22 +3406,22 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>CASE-007</t>
+          <t>PAT-009</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Patient Case File</t>
+          <t>Patient Directory</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Add Procedure Step to Treatment Plan</t>
+          <t>Sort Patients Table by Age</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>Check option to add treatment step</t>
+          <t>Click table column header to sort by patient age</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
@@ -3393,11 +3435,11 @@
         </is>
       </c>
       <c r="G60" s="9" t="n">
-        <v>0.006</v>
+        <v>3.059</v>
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>15:32:14</t>
+          <t>19:40:24</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr"/>
@@ -3405,22 +3447,22 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>CASE-008</t>
+          <t>PAT-010</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Patient Case File</t>
+          <t>Patient Directory</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Diagnostic Records &amp; X-rays Sub-Tab</t>
+          <t>Sort Patients Table by Last Visit</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>Switch to Records / Radiographs sub-tab</t>
+          <t>Click table column header to sort by last visit date</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -3434,11 +3476,11 @@
         </is>
       </c>
       <c r="G61" s="9" t="n">
-        <v>3.015</v>
+        <v>3.024</v>
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>15:32:14</t>
+          <t>19:40:27</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr"/>
@@ -3446,22 +3488,22 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>CASE-009</t>
+          <t>PAT-011</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Patient Case File</t>
+          <t>Patient Directory</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Collaboration &amp; Clinical Notes Sub-Tab</t>
+          <t>Open Add New Patient Modal</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Switch to Collaboration / Specialist notes sub-tab</t>
+          <t>Click '+ Add Patient' or 'New Patient' button</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
@@ -3475,11 +3517,11 @@
         </is>
       </c>
       <c r="G62" s="9" t="n">
-        <v>6.073</v>
+        <v>3.054</v>
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>15:32:17</t>
+          <t>19:40:30</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr"/>
@@ -3487,22 +3529,22 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>CASE-010</t>
+          <t>PAT-012</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Patient Case File</t>
+          <t>Patient Directory</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Prescriptions Sub-Tab</t>
+          <t>Add Patient Modal - Name Input</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>Switch to Prescriptions sub-tab</t>
+          <t>Fill patient full name in modal input</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -3516,11 +3558,11 @@
         </is>
       </c>
       <c r="G63" s="9" t="n">
-        <v>0.154</v>
+        <v>0.259</v>
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>15:32:23</t>
+          <t>19:40:33</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr"/>
@@ -3528,22 +3570,22 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>CASE-011</t>
+          <t>PAT-013</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Patient Case File</t>
+          <t>Patient Directory</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Lab Orders Sub-Tab</t>
+          <t>Add Patient Modal - Age Input</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Switch to Lab Orders sub-tab</t>
+          <t>Input patient age in number field</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -3557,11 +3599,11 @@
         </is>
       </c>
       <c r="G64" s="9" t="n">
-        <v>0.033</v>
+        <v>0.059</v>
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>15:32:23</t>
+          <t>19:40:33</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr"/>
@@ -3569,22 +3611,22 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>CASE-012</t>
+          <t>PAT-014</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Patient Case File</t>
+          <t>Patient Directory</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Export Patient Case Summary / PDF</t>
+          <t>Add Patient Modal - Gender Select</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>Verify print/export button for full case file</t>
+          <t>Select gender option (Female/Male)</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -3598,11 +3640,11 @@
         </is>
       </c>
       <c r="G65" s="9" t="n">
-        <v>9.048999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>15:32:23</t>
+          <t>19:40:33</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr"/>
@@ -3610,22 +3652,22 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>PRED-001</t>
+          <t>PAT-015</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>AI Predictor</t>
+          <t>Patient Directory</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Navigate to AI Predictor Screen</t>
+          <t>Add Patient Modal - Phone Input</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Open AI Predictor tab and check risk input form</t>
+          <t>Input contact phone number</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -3639,11 +3681,11 @@
         </is>
       </c>
       <c r="G66" s="9" t="n">
-        <v>6.027</v>
+        <v>0.137</v>
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
-          <t>15:32:35</t>
+          <t>19:40:33</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr"/>
@@ -3651,22 +3693,22 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>PRED-002</t>
+          <t>PAT-016</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>AI Predictor</t>
+          <t>Patient Directory</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Select Pulp Status Dropdown Option</t>
+          <t>Add Patient Modal - Tooth Selection</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>Select pulp status diagnosis dropdown</t>
+          <t>Select tooth number dropdown/picker</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -3680,11 +3722,11 @@
         </is>
       </c>
       <c r="G67" s="9" t="n">
-        <v>3.047</v>
+        <v>0.007</v>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
-          <t>15:32:41</t>
+          <t>19:40:33</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr"/>
@@ -3692,22 +3734,22 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>PRED-003</t>
+          <t>PAT-017</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>AI Predictor</t>
+          <t>Patient Directory</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Select Periapical Condition Option</t>
+          <t>Add Patient Modal - Diagnosis Selection</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>Set periapical status option</t>
+          <t>Select diagnosis type (e.g., Irreversible Pulpitis)</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
@@ -3721,11 +3763,11 @@
         </is>
       </c>
       <c r="G68" s="9" t="n">
-        <v>6.065</v>
+        <v>0.004</v>
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
-          <t>15:32:44</t>
+          <t>19:40:33</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr"/>
@@ -3733,22 +3775,22 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>PRED-004</t>
+          <t>PAT-018</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>AI Predictor</t>
+          <t>Patient Directory</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Adjust Pain Scale Slider (0-10)</t>
+          <t>Close / Cancel Add Patient Modal</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>Set patient pain level slider</t>
+          <t>Dismiss patient modal dialog</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
@@ -3762,11 +3804,11 @@
         </is>
       </c>
       <c r="G69" s="9" t="n">
-        <v>3.061</v>
+        <v>0.728</v>
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
-          <t>15:32:50</t>
+          <t>19:40:33</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr"/>
@@ -3774,22 +3816,22 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>PRED-005</t>
+          <t>CASE-001</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>AI Predictor</t>
+          <t>Patient Case File</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Toggle Medical History Risk: Diabetes</t>
+          <t>Open Patient Case File Main View</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Toggle systemic condition checkbox for Diabetes</t>
+          <t>Navigate to Patient Case File module</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
@@ -3803,11 +3845,11 @@
         </is>
       </c>
       <c r="G70" s="9" t="n">
-        <v>3.06</v>
+        <v>3.016</v>
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>15:32:53</t>
+          <t>19:40:35</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr"/>
@@ -3815,22 +3857,22 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>PRED-006</t>
+          <t>CASE-002</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>AI Predictor</t>
+          <t>Patient Case File</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Toggle Medical History Risk: Smoking</t>
+          <t>Demographics Sub-Tab</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>Toggle risk factor checkbox for Smoking</t>
+          <t>Switch to Demographics sub-tab</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
@@ -3844,11 +3886,11 @@
         </is>
       </c>
       <c r="G71" s="9" t="n">
-        <v>3.016</v>
+        <v>3.042</v>
       </c>
       <c r="H71" s="9" t="inlineStr">
         <is>
-          <t>15:32:57</t>
+          <t>19:40:38</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr"/>
@@ -3856,22 +3898,22 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>PRED-007</t>
+          <t>CASE-003</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>AI Predictor</t>
+          <t>Patient Case File</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Toggle Risk Factor: Prior Root Canal</t>
+          <t>Clinical History Sub-Tab</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>Toggle retreatment indicator checkbox</t>
+          <t>Switch to Clinical History sub-tab</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
@@ -3885,11 +3927,11 @@
         </is>
       </c>
       <c r="G72" s="9" t="n">
-        <v>6.021</v>
+        <v>0.027</v>
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>15:33:00</t>
+          <t>19:40:41</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr"/>
@@ -3897,22 +3939,22 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>PRED-008</t>
+          <t>CASE-004</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>AI Predictor</t>
+          <t>Patient Case File</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Click 'Run AI Risk Assessment' Button</t>
+          <t>Edit Medical History Notes Field</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>Trigger machine learning prediction algorithm button</t>
+          <t>Verify editable medical history text area</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
@@ -3926,11 +3968,11 @@
         </is>
       </c>
       <c r="G73" s="9" t="n">
-        <v>6.018</v>
+        <v>0.007</v>
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>15:33:06</t>
+          <t>19:40:41</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr"/>
@@ -3938,22 +3980,22 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>PRED-009</t>
+          <t>CASE-005</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>AI Predictor</t>
+          <t>Patient Case File</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Verify AI Risk Score Gauge Output</t>
+          <t>Edit Allergies &amp; Risk Factors Notes</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Ensure prediction result calculates numerical risk score %</t>
+          <t>Verify allergies &amp; drug hypersensitivity field</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
@@ -3967,11 +4009,11 @@
         </is>
       </c>
       <c r="G74" s="9" t="n">
-        <v>0.516</v>
+        <v>6.067</v>
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>15:33:12</t>
+          <t>19:40:41</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr"/>
@@ -3979,22 +4021,22 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>PRED-010</t>
+          <t>CASE-006</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>AI Predictor</t>
+          <t>Patient Case File</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Verify Flare-up Risk Category Badge</t>
+          <t>Treatment Planning Sub-Tab</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>Verify risk categorization badge</t>
+          <t>Switch to Treatment Planning sub-tab</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
@@ -4008,11 +4050,11 @@
         </is>
       </c>
       <c r="G75" s="9" t="n">
-        <v>9.173</v>
+        <v>3.027</v>
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
-          <t>15:33:12</t>
+          <t>19:40:47</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr"/>
@@ -4020,22 +4062,22 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>PRED-011</t>
+          <t>CASE-007</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>AI Predictor</t>
+          <t>Patient Case File</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Verify AI Treatment Recommendations Text</t>
+          <t>Add Procedure Step to Treatment Plan</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Ensure treatment protocol recommendations display</t>
+          <t>Check option to add treatment step</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
@@ -4049,11 +4091,11 @@
         </is>
       </c>
       <c r="G76" s="9" t="n">
-        <v>9.147</v>
+        <v>0.007</v>
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
-          <t>15:33:21</t>
+          <t>19:40:50</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr"/>
@@ -4061,22 +4103,22 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>PRED-012</t>
+          <t>CASE-008</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>AI Predictor</t>
+          <t>Patient Case File</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Export Prediction Report Summary</t>
+          <t>Mark Procedure Step as Complete</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>Verify export analysis option for prediction output</t>
+          <t>Toggle checkbox for completed procedure step</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
@@ -4090,11 +4132,11 @@
         </is>
       </c>
       <c r="G77" s="9" t="n">
-        <v>6.096</v>
+        <v>3.059</v>
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
-          <t>15:33:30</t>
+          <t>19:40:50</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr"/>
@@ -4102,22 +4144,22 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>ANAL-001</t>
+          <t>CASE-009</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Patient Case File</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Navigate to Analytics Screen</t>
+          <t>Diagnostic Records &amp; X-rays Sub-Tab</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Open Analytics tab and verify metrics</t>
+          <t>Switch to Records / Radiographs sub-tab</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
@@ -4131,11 +4173,11 @@
         </is>
       </c>
       <c r="G78" s="9" t="n">
-        <v>9.182</v>
+        <v>3.057</v>
       </c>
       <c r="H78" s="9" t="inlineStr">
         <is>
-          <t>15:33:40</t>
+          <t>19:40:53</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr"/>
@@ -4143,22 +4185,22 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>ANAL-002</t>
+          <t>CASE-010</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Patient Case File</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Verify Treatment Success Rate Metric</t>
+          <t>X-ray Image Zoom &amp; Pan Preview</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>Ensure treatment success percentage metric card displays</t>
+          <t>Click radiograph thumbnail for high-res preview modal</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
@@ -4172,11 +4214,11 @@
         </is>
       </c>
       <c r="G79" s="9" t="n">
-        <v>3.048</v>
+        <v>0.007</v>
       </c>
       <c r="H79" s="9" t="inlineStr">
         <is>
-          <t>15:33:49</t>
+          <t>19:40:56</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr"/>
@@ -4184,22 +4226,22 @@
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>ANAL-003</t>
+          <t>CASE-011</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Patient Case File</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Verify Pain Reduction Index Metric</t>
+          <t>Collaboration &amp; Clinical Notes Sub-Tab</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Check post-op pain reduction score display</t>
+          <t>Switch to Collaboration / Specialist notes sub-tab</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
@@ -4213,11 +4255,11 @@
         </is>
       </c>
       <c r="G80" s="9" t="n">
-        <v>6.071</v>
+        <v>6.044</v>
       </c>
       <c r="H80" s="9" t="inlineStr">
         <is>
-          <t>15:33:52</t>
+          <t>19:40:56</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr"/>
@@ -4225,22 +4267,22 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>ANAL-004</t>
+          <t>CASE-012</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Patient Case File</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Verify Canal Complexity Distribution Chart</t>
+          <t>Add Inter-disciplinary Specialist Note</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>Verify breakdown of simple vs complex canal anatomies</t>
+          <t>Input clinical referral note for endodontist</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
@@ -4254,11 +4296,11 @@
         </is>
       </c>
       <c r="G81" s="9" t="n">
-        <v>6.062</v>
+        <v>0.015</v>
       </c>
       <c r="H81" s="9" t="inlineStr">
         <is>
-          <t>15:33:58</t>
+          <t>19:41:02</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr"/>
@@ -4266,22 +4308,22 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>ANAL-005</t>
+          <t>CASE-013</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Patient Case File</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Verify Patient Demographics Chart</t>
+          <t>Prescriptions Sub-Tab</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>Check patient age and gender distribution visualization</t>
+          <t>Switch to Prescriptions sub-tab</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
@@ -4295,11 +4337,11 @@
         </is>
       </c>
       <c r="G82" s="9" t="n">
-        <v>6.096</v>
+        <v>0.068</v>
       </c>
       <c r="H82" s="9" t="inlineStr">
         <is>
-          <t>15:34:04</t>
+          <t>19:41:02</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr"/>
@@ -4307,22 +4349,22 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>ANAL-006</t>
+          <t>CASE-014</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Patient Case File</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Filter Analytics Timeframe</t>
+          <t>Add New Medication Prescription</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>Test timeframe selector (Month / Year)</t>
+          <t>Select analgesic / antibiotic prescription item</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
@@ -4336,11 +4378,11 @@
         </is>
       </c>
       <c r="G83" s="9" t="n">
-        <v>6.074</v>
+        <v>0.008</v>
       </c>
       <c r="H83" s="9" t="inlineStr">
         <is>
-          <t>15:34:10</t>
+          <t>19:41:02</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr"/>
@@ -4348,22 +4390,22 @@
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>ANAL-007</t>
+          <t>CASE-015</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Patient Case File</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Verify Practice Volume / Revenue Summary</t>
+          <t>Lab Orders Sub-Tab</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Check procedure volume numbers and throughput stats</t>
+          <t>Switch to Lab Orders sub-tab</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
@@ -4377,11 +4419,11 @@
         </is>
       </c>
       <c r="G84" s="9" t="n">
-        <v>6.084</v>
+        <v>0.034</v>
       </c>
       <c r="H84" s="9" t="inlineStr">
         <is>
-          <t>15:34:16</t>
+          <t>19:41:02</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr"/>
@@ -4389,22 +4431,22 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>ANAL-008</t>
+          <t>CASE-016</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Patient Case File</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Export Analytics Report</t>
+          <t>Create Digital Crown/Post Lab Order</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>Verify report export action button on Analytics page</t>
+          <t>Verify lab work requisition order form</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
@@ -4418,11 +4460,11 @@
         </is>
       </c>
       <c r="G85" s="9" t="n">
-        <v>3.039</v>
+        <v>6.066</v>
       </c>
       <c r="H85" s="9" t="inlineStr">
         <is>
-          <t>15:34:22</t>
+          <t>19:41:02</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr"/>
@@ -4430,22 +4472,22 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>AIAS-001</t>
+          <t>CASE-017</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>AI Assistant</t>
+          <t>Patient Case File</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Navigate to AI Assistant Screen</t>
+          <t>Print Patient Case Summary</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Open AI Assistant screen and check chat container</t>
+          <t>Trigger browser print view for clinical records</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
@@ -4459,11 +4501,11 @@
         </is>
       </c>
       <c r="G86" s="9" t="n">
-        <v>9.106999999999999</v>
+        <v>3.041</v>
       </c>
       <c r="H86" s="9" t="inlineStr">
         <is>
-          <t>15:34:29</t>
+          <t>19:41:08</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr"/>
@@ -4471,22 +4513,22 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>AIAS-002</t>
+          <t>CASE-018</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>AI Assistant</t>
+          <t>Patient Case File</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Verify Initial AI Welcome Message</t>
+          <t>Export Patient Case File PDF</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>Ensure welcome prompt from EndoPredict AI is present</t>
+          <t>Verify export button for full case file PDF summary</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
@@ -4500,11 +4542,11 @@
         </is>
       </c>
       <c r="G87" s="9" t="n">
-        <v>0.007</v>
+        <v>6.043</v>
       </c>
       <c r="H87" s="9" t="inlineStr">
         <is>
-          <t>15:34:38</t>
+          <t>19:41:11</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr"/>
@@ -4512,22 +4554,22 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>AIAS-003</t>
+          <t>PRED-001</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>AI Assistant</t>
+          <t>AI Predictor</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Click Quick Suggestion Prompt 1</t>
+          <t>Navigate to AI Predictor Screen</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>Click quick suggestion prompt pill</t>
+          <t>Open AI Predictor tab and check risk input form</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
@@ -4541,11 +4583,11 @@
         </is>
       </c>
       <c r="G88" s="9" t="n">
-        <v>6.073</v>
+        <v>6.061</v>
       </c>
       <c r="H88" s="9" t="inlineStr">
         <is>
-          <t>15:34:38</t>
+          <t>19:41:21</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr"/>
@@ -4553,22 +4595,22 @@
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>AIAS-004</t>
+          <t>PRED-002</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>AI Assistant</t>
+          <t>AI Predictor</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Verify AI Response Generated</t>
+          <t>Phone Input Patient Verification</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>Check that assistant responds to query message</t>
+          <t>Type patient phone number in risk calculator</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
@@ -4582,11 +4624,11 @@
         </is>
       </c>
       <c r="G89" s="9" t="n">
-        <v>0.516</v>
+        <v>3.043</v>
       </c>
       <c r="H89" s="9" t="inlineStr">
         <is>
-          <t>15:34:44</t>
+          <t>19:41:27</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr"/>
@@ -4594,22 +4636,22 @@
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>AIAS-005</t>
+          <t>PRED-003</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>AI Assistant</t>
+          <t>AI Predictor</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Type Custom Clinical Query into Chat Input</t>
+          <t>Select Tooth Number Dropdown Option</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Input clinical question into chat input field</t>
+          <t>Select tooth number diagnosis dropdown</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
@@ -4623,11 +4665,11 @@
         </is>
       </c>
       <c r="G90" s="9" t="n">
-        <v>3.043</v>
+        <v>3.058</v>
       </c>
       <c r="H90" s="9" t="inlineStr">
         <is>
-          <t>15:34:45</t>
+          <t>19:41:30</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr"/>
@@ -4635,22 +4677,22 @@
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>AIAS-006</t>
+          <t>PRED-004</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>AI Assistant</t>
+          <t>AI Predictor</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Click Send Button</t>
+          <t>Select Gender Option Dropdown</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>Click Send arrow icon button to submit prompt</t>
+          <t>Set patient gender dropdown selection</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
@@ -4664,11 +4706,11 @@
         </is>
       </c>
       <c r="G91" s="9" t="n">
-        <v>6.029</v>
+        <v>6.061</v>
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
-          <t>15:34:48</t>
+          <t>19:41:33</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr"/>
@@ -4676,22 +4718,22 @@
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>AIAS-007</t>
+          <t>PRED-005</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>AI Assistant</t>
+          <t>AI Predictor</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Clear Chat Conversation Button</t>
+          <t>Select Pulp Status Diagnosis</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>Test option to clear chat thread</t>
+          <t>Select pulp condition (e.g. Irreversible Pulpitis)</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
@@ -4705,11 +4747,11 @@
         </is>
       </c>
       <c r="G92" s="9" t="n">
-        <v>3.024</v>
+        <v>3.003</v>
       </c>
       <c r="H92" s="9" t="inlineStr">
         <is>
-          <t>15:34:54</t>
+          <t>19:41:39</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr"/>
@@ -4717,22 +4759,22 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>AIAS-008</t>
+          <t>PRED-006</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>AI Assistant</t>
+          <t>AI Predictor</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Download Chat Log</t>
+          <t>Select Periapical Condition Option</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>Verify download transcript option for AI consultation session</t>
+          <t>Set periapical status option (e.g. Normal / Apical Periodontitis)</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
@@ -4746,11 +4788,11 @@
         </is>
       </c>
       <c r="G93" s="9" t="n">
-        <v>6.055</v>
+        <v>6.119</v>
       </c>
       <c r="H93" s="9" t="inlineStr">
         <is>
-          <t>15:34:57</t>
+          <t>19:41:42</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr"/>
@@ -4758,22 +4800,22 @@
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>APPT-001</t>
+          <t>PRED-007</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Appointments</t>
+          <t>AI Predictor</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Navigate to Appointments Screen</t>
+          <t>Adjust Pain Scale Slider (0-10)</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Open Appointments calendar view</t>
+          <t>Set patient pain level slider</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
@@ -4787,11 +4829,11 @@
         </is>
       </c>
       <c r="G94" s="9" t="n">
-        <v>9.130000000000001</v>
+        <v>3.056</v>
       </c>
       <c r="H94" s="9" t="inlineStr">
         <is>
-          <t>15:35:06</t>
+          <t>19:41:48</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr"/>
@@ -4799,22 +4841,22 @@
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>APPT-002</t>
+          <t>PRED-008</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>Appointments</t>
+          <t>AI Predictor</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Open Schedule New Appointment Modal</t>
+          <t>Select Swelling Severity Option</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>Click '+ New Appointment' or 'Schedule' button</t>
+          <t>Select facial/localized swelling level (None / Mild / Severe)</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
@@ -4828,11 +4870,11 @@
         </is>
       </c>
       <c r="G95" s="9" t="n">
-        <v>6.066</v>
+        <v>3.047</v>
       </c>
       <c r="H95" s="9" t="inlineStr">
         <is>
-          <t>15:35:15</t>
+          <t>19:41:51</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr"/>
@@ -4840,22 +4882,22 @@
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>APPT-003</t>
+          <t>PRED-009</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>Appointments</t>
+          <t>AI Predictor</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Select Patient for Appointment</t>
+          <t>Select Treatment Protocol Type</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>Select patient name from dropdown/input</t>
+          <t>Select Single Visit vs Multi-Visit treatment protocol</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
@@ -4869,11 +4911,11 @@
         </is>
       </c>
       <c r="G96" s="9" t="n">
-        <v>3.032</v>
+        <v>6.1</v>
       </c>
       <c r="H96" s="9" t="inlineStr">
         <is>
-          <t>15:35:21</t>
+          <t>19:41:54</t>
         </is>
       </c>
       <c r="I96" s="10" t="inlineStr"/>
@@ -4881,22 +4923,22 @@
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>APPT-004</t>
+          <t>PRED-010</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>Appointments</t>
+          <t>AI Predictor</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Select Date &amp; Time for Appointment</t>
+          <t>Toggle Systemic Risk: Diabetes Mellitus</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>Pick appointment date and time slot</t>
+          <t>Toggle systemic condition checkbox for Diabetes</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
@@ -4910,11 +4952,11 @@
         </is>
       </c>
       <c r="G97" s="9" t="n">
-        <v>3.042</v>
+        <v>3.036</v>
       </c>
       <c r="H97" s="9" t="inlineStr">
         <is>
-          <t>15:35:24</t>
+          <t>19:42:00</t>
         </is>
       </c>
       <c r="I97" s="10" t="inlineStr"/>
@@ -4922,22 +4964,22 @@
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>APPT-005</t>
+          <t>PRED-011</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>Appointments</t>
+          <t>AI Predictor</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Select Procedure Type</t>
+          <t>Toggle Systemic Risk: Tobacco / Smoking</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>Select treatment procedure option</t>
+          <t>Toggle risk factor checkbox for Smoking</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
@@ -4951,11 +4993,11 @@
         </is>
       </c>
       <c r="G98" s="9" t="n">
-        <v>6.084</v>
+        <v>3.018</v>
       </c>
       <c r="H98" s="9" t="inlineStr">
         <is>
-          <t>15:35:27</t>
+          <t>19:42:03</t>
         </is>
       </c>
       <c r="I98" s="10" t="inlineStr"/>
@@ -4963,22 +5005,22 @@
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>APPT-006</t>
+          <t>PRED-012</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>Appointments</t>
+          <t>AI Predictor</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Submit Schedule Appointment Form</t>
+          <t>Toggle Risk Factor: Prior Root Canal Retreatment</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>Click Save / Schedule appointment button</t>
+          <t>Toggle retreatment indicator checkbox</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
@@ -4992,11 +5034,11 @@
         </is>
       </c>
       <c r="G99" s="9" t="n">
-        <v>3.049</v>
+        <v>6.044</v>
       </c>
       <c r="H99" s="9" t="inlineStr">
         <is>
-          <t>15:35:33</t>
+          <t>19:42:06</t>
         </is>
       </c>
       <c r="I99" s="10" t="inlineStr"/>
@@ -5004,22 +5046,22 @@
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>APPT-007</t>
+          <t>PRED-013</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>Appointments</t>
+          <t>AI Predictor</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Verify Scheduled Appointment in List</t>
+          <t>Toggle Systemic Risk: Hypertension</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>Ensure newly scheduled appointment appears in list view</t>
+          <t>Toggle hypertension vascular risk factor checkbox</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
@@ -5033,11 +5075,11 @@
         </is>
       </c>
       <c r="G100" s="9" t="n">
-        <v>6.068</v>
+        <v>3.028</v>
       </c>
       <c r="H100" s="9" t="inlineStr">
         <is>
-          <t>15:35:36</t>
+          <t>19:42:12</t>
         </is>
       </c>
       <c r="I100" s="10" t="inlineStr"/>
@@ -5045,22 +5087,22 @@
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>APPT-008</t>
+          <t>PRED-014</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>Appointments</t>
+          <t>AI Predictor</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Filter Appointments by Status</t>
+          <t>Click 'Run AI Risk Assessment' Button</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>Filter schedule by Upcoming vs Completed appointments</t>
+          <t>Trigger machine learning prediction algorithm button</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
@@ -5074,11 +5116,11 @@
         </is>
       </c>
       <c r="G101" s="9" t="n">
-        <v>6.103</v>
+        <v>6.105</v>
       </c>
       <c r="H101" s="9" t="inlineStr">
         <is>
-          <t>15:35:43</t>
+          <t>19:42:15</t>
         </is>
       </c>
       <c r="I101" s="10" t="inlineStr"/>
@@ -5086,22 +5128,22 @@
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>SETT-001</t>
+          <t>PRED-015</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>AI Predictor</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Navigate to Settings Screen</t>
+          <t>Verify AI Risk Score Gauge Output</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Open Settings page and verify options</t>
+          <t>Ensure prediction result calculates numerical risk score %</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
@@ -5115,11 +5157,11 @@
         </is>
       </c>
       <c r="G102" s="9" t="n">
-        <v>9.116</v>
+        <v>0.517</v>
       </c>
       <c r="H102" s="9" t="inlineStr">
         <is>
-          <t>15:35:52</t>
+          <t>19:42:22</t>
         </is>
       </c>
       <c r="I102" s="10" t="inlineStr"/>
@@ -5127,22 +5169,22 @@
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>SETT-002</t>
+          <t>PRED-016</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>AI Predictor</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Change Default Tooth Numbering System</t>
+          <t>Verify Flare-up Risk Category Badge</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>Change numbering system select option (FDI / Universal)</t>
+          <t>Verify risk categorization badge (High / Moderate / Low)</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
@@ -5156,11 +5198,11 @@
         </is>
       </c>
       <c r="G103" s="9" t="n">
-        <v>6.043</v>
+        <v>9.074</v>
       </c>
       <c r="H103" s="9" t="inlineStr">
         <is>
-          <t>15:36:01</t>
+          <t>19:42:22</t>
         </is>
       </c>
       <c r="I103" s="10" t="inlineStr"/>
@@ -5168,22 +5210,22 @@
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>SETT-003</t>
+          <t>PRED-017</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>AI Predictor</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Update Doctor Profile / Clinic Information</t>
+          <t>Verify AI Treatment Recommendations Text</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Verify editable fields for Doctor Name, License, Clinic Title</t>
+          <t>Ensure evidence-based treatment recommendations display</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
@@ -5197,11 +5239,11 @@
         </is>
       </c>
       <c r="G104" s="9" t="n">
-        <v>9.124000000000001</v>
+        <v>9.143000000000001</v>
       </c>
       <c r="H104" s="9" t="inlineStr">
         <is>
-          <t>15:36:07</t>
+          <t>19:42:31</t>
         </is>
       </c>
       <c r="I104" s="10" t="inlineStr"/>
@@ -5209,22 +5251,22 @@
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>SETT-004</t>
+          <t>PRED-018</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>AI Predictor</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Toggle Dark Mode Theme Switcher from Settings</t>
+          <t>Export Prediction Report Summary</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>Click theme toggle switch inside settings panel</t>
+          <t>Verify export analysis option for prediction output</t>
         </is>
       </c>
       <c r="E105" s="9" t="inlineStr">
@@ -5238,11 +5280,11 @@
         </is>
       </c>
       <c r="G105" s="9" t="n">
-        <v>6.058</v>
+        <v>6.1</v>
       </c>
       <c r="H105" s="9" t="inlineStr">
         <is>
-          <t>15:36:16</t>
+          <t>19:42:40</t>
         </is>
       </c>
       <c r="I105" s="10" t="inlineStr"/>
@@ -5250,22 +5292,22 @@
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>SETT-005</t>
+          <t>ANAL-001</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Export Local Database Backup JSON</t>
+          <t>Navigate to Analytics Screen</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Click Backup / Export DB button to generate backup file</t>
+          <t>Open Analytics tab and verify metrics</t>
         </is>
       </c>
       <c r="E106" s="9" t="inlineStr">
@@ -5279,11 +5321,11 @@
         </is>
       </c>
       <c r="G106" s="9" t="n">
-        <v>6.064</v>
+        <v>3.032</v>
       </c>
       <c r="H106" s="9" t="inlineStr">
         <is>
-          <t>15:36:22</t>
+          <t>19:42:50</t>
         </is>
       </c>
       <c r="I106" s="10" t="inlineStr"/>
@@ -5291,22 +5333,22 @@
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>SETT-006</t>
+          <t>ANAL-002</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Verify Local Storage DB Status Indicator</t>
+          <t>Verify Treatment Success Rate Metric</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>Check local IndexedDB / Storage health status message</t>
+          <t>Ensure treatment success percentage metric card displays</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
@@ -5320,11 +5362,11 @@
         </is>
       </c>
       <c r="G107" s="9" t="n">
-        <v>9.156000000000001</v>
+        <v>3.065</v>
       </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
-          <t>15:36:28</t>
+          <t>19:42:53</t>
         </is>
       </c>
       <c r="I107" s="10" t="inlineStr"/>
@@ -5332,22 +5374,22 @@
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>SETT-007</t>
+          <t>ANAL-003</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Save System Preferences Button</t>
+          <t>Verify Pain Reduction Index Metric</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>Click Save Preferences button</t>
+          <t>Check post-op pain reduction score display</t>
         </is>
       </c>
       <c r="E108" s="9" t="inlineStr">
@@ -5361,11 +5403,11 @@
         </is>
       </c>
       <c r="G108" s="9" t="n">
-        <v>3.053</v>
+        <v>6.067</v>
       </c>
       <c r="H108" s="9" t="inlineStr">
         <is>
-          <t>15:36:38</t>
+          <t>19:42:56</t>
         </is>
       </c>
       <c r="I108" s="10" t="inlineStr"/>
@@ -5373,22 +5415,22 @@
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>SETT-008</t>
+          <t>ANAL-004</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Verify App Build Version &amp; Information</t>
+          <t>Verify Canal Complexity Distribution Chart</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>Check software version label (v1.0.0 / EndoPredict AI)</t>
+          <t>Verify breakdown of simple vs complex canal anatomies</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
@@ -5402,11 +5444,11 @@
         </is>
       </c>
       <c r="G109" s="9" t="n">
-        <v>0.006</v>
+        <v>6.09</v>
       </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>15:36:41</t>
+          <t>19:43:02</t>
         </is>
       </c>
       <c r="I109" s="10" t="inlineStr"/>
@@ -5414,22 +5456,22 @@
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>AUTH-001</t>
+          <t>ANAL-005</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Open User Profile / Doctor Settings</t>
+          <t>Verify Patient Demographics Chart</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Verify Doctor Clinical Profile settings panel</t>
+          <t>Check patient age and gender distribution visualization</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
@@ -5443,11 +5485,11 @@
         </is>
       </c>
       <c r="G110" s="9" t="n">
-        <v>6.029</v>
+        <v>6.037</v>
       </c>
       <c r="H110" s="9" t="inlineStr">
         <is>
-          <t>15:36:41</t>
+          <t>19:43:08</t>
         </is>
       </c>
       <c r="I110" s="10" t="inlineStr"/>
@@ -5455,22 +5497,22 @@
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>AUTH-002</t>
+          <t>ANAL-006</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Verify Doctor Credentials in Profile</t>
+          <t>Timeframe Filter: 1 Month</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>Verify profile card displays practitioner credentials</t>
+          <t>Select 1 month timeframe filter option</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
@@ -5484,11 +5526,11 @@
         </is>
       </c>
       <c r="G111" s="9" t="n">
-        <v>6.1</v>
+        <v>6.066</v>
       </c>
       <c r="H111" s="9" t="inlineStr">
         <is>
-          <t>15:36:47</t>
+          <t>19:43:14</t>
         </is>
       </c>
       <c r="I111" s="10" t="inlineStr"/>
@@ -5496,22 +5538,22 @@
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>AUTH-003</t>
+          <t>ANAL-007</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Test Logout Action</t>
+          <t>Timeframe Filter: 6 Months</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>Click Logout button to exit session</t>
+          <t>Select 6 months timeframe filter option</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
@@ -5525,11 +5567,11 @@
         </is>
       </c>
       <c r="G112" s="9" t="n">
-        <v>3.023</v>
+        <v>6.084</v>
       </c>
       <c r="H112" s="9" t="inlineStr">
         <is>
-          <t>15:36:53</t>
+          <t>19:43:20</t>
         </is>
       </c>
       <c r="I112" s="10" t="inlineStr"/>
@@ -5537,22 +5579,22 @@
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>AUTH-004</t>
+          <t>ANAL-008</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Verify Doctor Login Screen Render</t>
+          <t>Timeframe Filter: 1 Year</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>Verify Login email &amp; password form display</t>
+          <t>Select 1 year timeframe filter option</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr">
@@ -5566,11 +5608,11 @@
         </is>
       </c>
       <c r="G113" s="9" t="n">
-        <v>6.059</v>
+        <v>6.091</v>
       </c>
       <c r="H113" s="9" t="inlineStr">
         <is>
-          <t>15:36:56</t>
+          <t>19:43:26</t>
         </is>
       </c>
       <c r="I113" s="10" t="inlineStr"/>
@@ -5578,22 +5620,22 @@
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>AUTH-005</t>
+          <t>ANAL-009</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Test Doctor Login Submit Flow</t>
+          <t>Verify Practice Volume / Revenue Summary</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Submit doctor demo login form to restore session</t>
+          <t>Check procedure volume numbers and throughput stats</t>
         </is>
       </c>
       <c r="E114" s="9" t="inlineStr">
@@ -5607,11 +5649,11 @@
         </is>
       </c>
       <c r="G114" s="9" t="n">
-        <v>7.3</v>
+        <v>6.078</v>
       </c>
       <c r="H114" s="9" t="inlineStr">
         <is>
-          <t>15:37:02</t>
+          <t>19:43:32</t>
         </is>
       </c>
       <c r="I114" s="10" t="inlineStr"/>
@@ -5619,22 +5661,22 @@
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>AUTH-006</t>
+          <t>ANAL-010</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Switch to Patient Portal Mode</t>
+          <t>Average Treatment Duration Metric</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>Test Patient Portal mode switch link</t>
+          <t>Check mean appointment duration stat</t>
         </is>
       </c>
       <c r="E115" s="9" t="inlineStr">
@@ -5648,11 +5690,11 @@
         </is>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3.051</v>
+        <v>6.092</v>
       </c>
       <c r="H115" s="9" t="inlineStr">
         <is>
-          <t>15:37:09</t>
+          <t>19:43:38</t>
         </is>
       </c>
       <c r="I115" s="10" t="inlineStr"/>
@@ -5660,22 +5702,22 @@
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>NOTIF-001</t>
+          <t>ANAL-011</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Open Notifications Dropdown</t>
+          <t>Flare-up Incident Rate Metric Card</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>Click header bell icon to open notifications popover</t>
+          <t>Check post-op emergency visit percentage metric</t>
         </is>
       </c>
       <c r="E116" s="9" t="inlineStr">
@@ -5689,11 +5731,11 @@
         </is>
       </c>
       <c r="G116" s="9" t="n">
-        <v>6.03</v>
+        <v>6.079</v>
       </c>
       <c r="H116" s="9" t="inlineStr">
         <is>
-          <t>15:37:12</t>
+          <t>19:43:44</t>
         </is>
       </c>
       <c r="I116" s="10" t="inlineStr"/>
@@ -5701,22 +5743,22 @@
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>NOTIF-002</t>
+          <t>ANAL-012</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>Verify Unread Notification Count Badge</t>
+          <t>Specialist Referral Percentage Metric</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>Check numerical unread alert badge overlay</t>
+          <t>Verify percentage of cases referred to endodontist</t>
         </is>
       </c>
       <c r="E117" s="9" t="inlineStr">
@@ -5730,11 +5772,11 @@
         </is>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3.018</v>
+        <v>3.055</v>
       </c>
       <c r="H117" s="9" t="inlineStr">
         <is>
-          <t>15:37:18</t>
+          <t>19:43:50</t>
         </is>
       </c>
       <c r="I117" s="10" t="inlineStr"/>
@@ -5742,22 +5784,22 @@
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>NOTIF-003</t>
+          <t>ANAL-013</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>Click Mark All as Read Button</t>
+          <t>Chart Tooltip Hover Interaction</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>Clear unread notification count badge</t>
+          <t>Hover over analytics chart bars/segments</t>
         </is>
       </c>
       <c r="E118" s="9" t="inlineStr">
@@ -5771,11 +5813,11 @@
         </is>
       </c>
       <c r="G118" s="9" t="n">
-        <v>3.008</v>
+        <v>3.046</v>
       </c>
       <c r="H118" s="9" t="inlineStr">
         <is>
-          <t>15:37:21</t>
+          <t>19:43:54</t>
         </is>
       </c>
       <c r="I118" s="10" t="inlineStr"/>
@@ -5783,22 +5825,22 @@
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>NOTIF-004</t>
+          <t>ANAL-014</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>Clear Notification List</t>
+          <t>Print Analytics Summary</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>Clear all notifications from list</t>
+          <t>Trigger browser print view for clinical analytics</t>
         </is>
       </c>
       <c r="E119" s="9" t="inlineStr">
@@ -5812,11 +5854,11 @@
         </is>
       </c>
       <c r="G119" s="9" t="n">
-        <v>3.028</v>
+        <v>3.044</v>
       </c>
       <c r="H119" s="9" t="inlineStr">
         <is>
-          <t>15:37:24</t>
+          <t>19:43:57</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr"/>
@@ -5824,22 +5866,22 @@
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>UI-001</t>
+          <t>ANAL-015</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>Theme &amp; Layout</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Toggle Dark Mode Theme Switcher</t>
+          <t>Export Analytics Report</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>Click Dark/Light theme toggle switch in sidebar</t>
+          <t>Verify report export action button on Analytics page</t>
         </is>
       </c>
       <c r="E120" s="9" t="inlineStr">
@@ -5853,11 +5895,11 @@
         </is>
       </c>
       <c r="G120" s="9" t="n">
-        <v>6.097</v>
+        <v>3.029</v>
       </c>
       <c r="H120" s="9" t="inlineStr">
         <is>
-          <t>15:37:27</t>
+          <t>19:44:00</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr"/>
@@ -5865,22 +5907,22 @@
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>UI-002</t>
+          <t>AIAS-001</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>Theme &amp; Layout</t>
+          <t>AI Assistant</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Verify Dark Mode Background Theme</t>
+          <t>Navigate to AI Assistant Screen</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>Check document body background styling changes</t>
+          <t>Open AI Assistant screen and check chat container</t>
         </is>
       </c>
       <c r="E121" s="9" t="inlineStr">
@@ -5894,11 +5936,11 @@
         </is>
       </c>
       <c r="G121" s="9" t="n">
-        <v>0.017</v>
+        <v>3.035</v>
       </c>
       <c r="H121" s="9" t="inlineStr">
         <is>
-          <t>15:37:33</t>
+          <t>19:44:06</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr"/>
@@ -5906,22 +5948,22 @@
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>UI-003</t>
+          <t>AIAS-002</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>Theme &amp; Layout</t>
+          <t>AI Assistant</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Toggle Back to Light Mode</t>
+          <t>Verify Initial AI Welcome Message</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>Click theme switch button again to revert to light theme</t>
+          <t>Ensure welcome prompt from EndoPredict AI is present</t>
         </is>
       </c>
       <c r="E122" s="9" t="inlineStr">
@@ -5935,11 +5977,11 @@
         </is>
       </c>
       <c r="G122" s="9" t="n">
-        <v>6.063</v>
+        <v>0.01</v>
       </c>
       <c r="H122" s="9" t="inlineStr">
         <is>
-          <t>15:37:33</t>
+          <t>19:44:09</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr"/>
@@ -5947,22 +5989,22 @@
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>UI-004</t>
+          <t>AIAS-003</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>Theme &amp; Layout</t>
+          <t>AI Assistant</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Mobile Viewport Test (Width 390px)</t>
+          <t>Quick Suggestion Pill 1: Analgesic Protocol</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>Resize browser window to mobile iPhone 12 Pro dimensions (390x844)</t>
+          <t>Click post-op pain management quick prompt pill</t>
         </is>
       </c>
       <c r="E123" s="9" t="inlineStr">
@@ -5976,11 +6018,11 @@
         </is>
       </c>
       <c r="G123" s="9" t="n">
-        <v>0.853</v>
+        <v>3.063</v>
       </c>
       <c r="H123" s="9" t="inlineStr">
         <is>
-          <t>15:37:39</t>
+          <t>19:44:09</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr"/>
@@ -5988,22 +6030,22 @@
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>UI-005</t>
+          <t>AIAS-004</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>Theme &amp; Layout</t>
+          <t>AI Assistant</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>Verify Mobile Bottom Navigation Bar</t>
+          <t>Quick Suggestion Pill 2: Pulpitis Differential</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>Ensure desktop sidebar hides and bottom mobile nav bar appears</t>
+          <t>Click pulpitis diagnosis quick prompt pill</t>
         </is>
       </c>
       <c r="E124" s="9" t="inlineStr">
@@ -6017,11 +6059,11 @@
         </is>
       </c>
       <c r="G124" s="9" t="n">
-        <v>3.06</v>
+        <v>3.035</v>
       </c>
       <c r="H124" s="9" t="inlineStr">
         <is>
-          <t>15:37:40</t>
+          <t>19:44:12</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr"/>
@@ -6029,43 +6071,4061 @@
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="9" t="inlineStr">
         <is>
+          <t>AIAS-005</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>AI Assistant</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>Quick Suggestion Pill 3: Irrigation Protocol</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>Click NaOCl irrigation quick prompt pill</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F125" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G125" s="9" t="n">
+        <v>3.073</v>
+      </c>
+      <c r="H125" s="9" t="inlineStr">
+        <is>
+          <t>19:44:15</t>
+        </is>
+      </c>
+      <c r="I125" s="10" t="inlineStr"/>
+    </row>
+    <row r="126" ht="22" customHeight="1">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>AIAS-006</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>AI Assistant</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>Verify AI Response Bubble Render</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="inlineStr">
+        <is>
+          <t>Check that assistant responds to query message</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>19:44:18</t>
+        </is>
+      </c>
+      <c r="I126" s="10" t="inlineStr"/>
+    </row>
+    <row r="127" ht="22" customHeight="1">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>AIAS-007</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>AI Assistant</t>
+        </is>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>Type Custom Clinical Query into Chat Input</t>
+        </is>
+      </c>
+      <c r="D127" s="10" t="inlineStr">
+        <is>
+          <t>Input clinical question into chat input field</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G127" s="9" t="n">
+        <v>3.005</v>
+      </c>
+      <c r="H127" s="9" t="inlineStr">
+        <is>
+          <t>19:44:19</t>
+        </is>
+      </c>
+      <c r="I127" s="10" t="inlineStr"/>
+    </row>
+    <row r="128" ht="22" customHeight="1">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>AIAS-008</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>AI Assistant</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>Click Send Arrow Button</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>Click Send arrow icon button to submit prompt</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G128" s="9" t="n">
+        <v>6.018</v>
+      </c>
+      <c r="H128" s="9" t="inlineStr">
+        <is>
+          <t>19:44:22</t>
+        </is>
+      </c>
+      <c r="I128" s="10" t="inlineStr"/>
+    </row>
+    <row r="129" ht="22" customHeight="1">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>AIAS-009</t>
+        </is>
+      </c>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>AI Assistant</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>Keyboard Enter Key Submit</t>
+        </is>
+      </c>
+      <c r="D129" s="10" t="inlineStr">
+        <is>
+          <t>Press Enter key in input field to submit message</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="9" t="inlineStr">
+        <is>
+          <t>19:44:28</t>
+        </is>
+      </c>
+      <c r="I129" s="10" t="inlineStr"/>
+    </row>
+    <row r="130" ht="22" customHeight="1">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>AIAS-010</t>
+        </is>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>AI Assistant</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
+          <t>Verify Chat Message Timestamp Display</t>
+        </is>
+      </c>
+      <c r="D130" s="10" t="inlineStr">
+        <is>
+          <t>Verify timestamp label on chat bubbles</t>
+        </is>
+      </c>
+      <c r="E130" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F130" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G130" s="9" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H130" s="9" t="inlineStr">
+        <is>
+          <t>19:44:28</t>
+        </is>
+      </c>
+      <c r="I130" s="10" t="inlineStr"/>
+    </row>
+    <row r="131" ht="22" customHeight="1">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>AIAS-011</t>
+        </is>
+      </c>
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>AI Assistant</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>Clear Chat Conversation Button</t>
+        </is>
+      </c>
+      <c r="D131" s="10" t="inlineStr">
+        <is>
+          <t>Test option to clear chat thread</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F131" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G131" s="9" t="n">
+        <v>3.044</v>
+      </c>
+      <c r="H131" s="9" t="inlineStr">
+        <is>
+          <t>19:44:28</t>
+        </is>
+      </c>
+      <c r="I131" s="10" t="inlineStr"/>
+    </row>
+    <row r="132" ht="22" customHeight="1">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>AIAS-012</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>AI Assistant</t>
+        </is>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
+          <t>Copy Response Text Action</t>
+        </is>
+      </c>
+      <c r="D132" s="10" t="inlineStr">
+        <is>
+          <t>Test copy response text to clipboard button</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G132" s="9" t="n">
+        <v>3.041</v>
+      </c>
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>19:44:31</t>
+        </is>
+      </c>
+      <c r="I132" s="10" t="inlineStr"/>
+    </row>
+    <row r="133" ht="22" customHeight="1">
+      <c r="A133" s="9" t="inlineStr">
+        <is>
+          <t>AIAS-013</t>
+        </is>
+      </c>
+      <c r="B133" s="10" t="inlineStr">
+        <is>
+          <t>AI Assistant</t>
+        </is>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
+        <is>
+          <t>Download Chat Log Consultation</t>
+        </is>
+      </c>
+      <c r="D133" s="10" t="inlineStr">
+        <is>
+          <t>Verify download transcript option for AI consultation session</t>
+        </is>
+      </c>
+      <c r="E133" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G133" s="9" t="n">
+        <v>6.102</v>
+      </c>
+      <c r="H133" s="9" t="inlineStr">
+        <is>
+          <t>19:44:34</t>
+        </is>
+      </c>
+      <c r="I133" s="10" t="inlineStr"/>
+    </row>
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>AIAS-014</t>
+        </is>
+      </c>
+      <c r="B134" s="10" t="inlineStr">
+        <is>
+          <t>AI Assistant</t>
+        </is>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
+          <t>Regenerate AI Response Trigger</t>
+        </is>
+      </c>
+      <c r="D134" s="10" t="inlineStr">
+        <is>
+          <t>Click regenerate response action button</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G134" s="9" t="n">
+        <v>3.031</v>
+      </c>
+      <c r="H134" s="9" t="inlineStr">
+        <is>
+          <t>19:44:40</t>
+        </is>
+      </c>
+      <c r="I134" s="10" t="inlineStr"/>
+    </row>
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>AIAS-015</t>
+        </is>
+      </c>
+      <c r="B135" s="10" t="inlineStr">
+        <is>
+          <t>AI Assistant</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>Switch AI Temperature / Model Mode</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="inlineStr">
+        <is>
+          <t>Check clinical vs creative AI model setting toggle</t>
+        </is>
+      </c>
+      <c r="E135" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G135" s="9" t="n">
+        <v>6.083</v>
+      </c>
+      <c r="H135" s="9" t="inlineStr">
+        <is>
+          <t>19:44:43</t>
+        </is>
+      </c>
+      <c r="I135" s="10" t="inlineStr"/>
+    </row>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>APPT-001</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>Navigate to Appointments Screen</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>Open Appointments calendar view</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G136" s="9" t="n">
+        <v>3.051</v>
+      </c>
+      <c r="H136" s="9" t="inlineStr">
+        <is>
+          <t>19:44:52</t>
+        </is>
+      </c>
+      <c r="I136" s="10" t="inlineStr"/>
+    </row>
+    <row r="137" ht="22" customHeight="1">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>APPT-002</t>
+        </is>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>Verify Today Date Highlight</t>
+        </is>
+      </c>
+      <c r="D137" s="10" t="inlineStr">
+        <is>
+          <t>Ensure current calendar date is highlighted</t>
+        </is>
+      </c>
+      <c r="E137" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G137" s="9" t="n">
+        <v>6.064</v>
+      </c>
+      <c r="H137" s="9" t="inlineStr">
+        <is>
+          <t>19:44:55</t>
+        </is>
+      </c>
+      <c r="I137" s="10" t="inlineStr"/>
+    </row>
+    <row r="138" ht="22" customHeight="1">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>APPT-003</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>Switch Calendar View: Month Mode</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>Switch to full month calendar layout</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G138" s="9" t="n">
+        <v>3.059</v>
+      </c>
+      <c r="H138" s="9" t="inlineStr">
+        <is>
+          <t>19:45:01</t>
+        </is>
+      </c>
+      <c r="I138" s="10" t="inlineStr"/>
+    </row>
+    <row r="139" ht="22" customHeight="1">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>APPT-004</t>
+        </is>
+      </c>
+      <c r="B139" s="10" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
+        <is>
+          <t>Switch Calendar View: Week Mode</t>
+        </is>
+      </c>
+      <c r="D139" s="10" t="inlineStr">
+        <is>
+          <t>Switch to week schedule layout</t>
+        </is>
+      </c>
+      <c r="E139" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G139" s="9" t="n">
+        <v>3.051</v>
+      </c>
+      <c r="H139" s="9" t="inlineStr">
+        <is>
+          <t>19:45:05</t>
+        </is>
+      </c>
+      <c r="I139" s="10" t="inlineStr"/>
+    </row>
+    <row r="140" ht="22" customHeight="1">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>APPT-005</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>Open Schedule New Appointment Modal</t>
+        </is>
+      </c>
+      <c r="D140" s="10" t="inlineStr">
+        <is>
+          <t>Click '+ New Appointment' or 'Schedule' button</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G140" s="9" t="n">
+        <v>6.109</v>
+      </c>
+      <c r="H140" s="9" t="inlineStr">
+        <is>
+          <t>19:45:08</t>
+        </is>
+      </c>
+      <c r="I140" s="10" t="inlineStr"/>
+    </row>
+    <row r="141" ht="22" customHeight="1">
+      <c r="A141" s="9" t="inlineStr">
+        <is>
+          <t>APPT-006</t>
+        </is>
+      </c>
+      <c r="B141" s="10" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
+        <is>
+          <t>Select Patient for Appointment</t>
+        </is>
+      </c>
+      <c r="D141" s="10" t="inlineStr">
+        <is>
+          <t>Select patient name from dropdown/input</t>
+        </is>
+      </c>
+      <c r="E141" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F141" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" s="9" t="inlineStr">
+        <is>
+          <t>19:45:14</t>
+        </is>
+      </c>
+      <c r="I141" s="10" t="inlineStr"/>
+    </row>
+    <row r="142" ht="22" customHeight="1">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>APPT-007</t>
+        </is>
+      </c>
+      <c r="B142" s="10" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
+        <is>
+          <t>Select Date &amp; Time Slot Input</t>
+        </is>
+      </c>
+      <c r="D142" s="10" t="inlineStr">
+        <is>
+          <t>Pick appointment date and time slot</t>
+        </is>
+      </c>
+      <c r="E142" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F142" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G142" s="9" t="n">
+        <v>3.043</v>
+      </c>
+      <c r="H142" s="9" t="inlineStr">
+        <is>
+          <t>19:45:14</t>
+        </is>
+      </c>
+      <c r="I142" s="10" t="inlineStr"/>
+    </row>
+    <row r="143" ht="22" customHeight="1">
+      <c r="A143" s="9" t="inlineStr">
+        <is>
+          <t>APPT-008</t>
+        </is>
+      </c>
+      <c r="B143" s="10" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C143" s="10" t="inlineStr">
+        <is>
+          <t>Select Procedure Type Dropdown</t>
+        </is>
+      </c>
+      <c r="D143" s="10" t="inlineStr">
+        <is>
+          <t>Select treatment procedure option (e.g. Root Canal Treatment)</t>
+        </is>
+      </c>
+      <c r="E143" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F143" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G143" s="9" t="n">
+        <v>6.106</v>
+      </c>
+      <c r="H143" s="9" t="inlineStr">
+        <is>
+          <t>19:45:17</t>
+        </is>
+      </c>
+      <c r="I143" s="10" t="inlineStr"/>
+    </row>
+    <row r="144" ht="22" customHeight="1">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>APPT-009</t>
+        </is>
+      </c>
+      <c r="B144" s="10" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>Input Clinical Notes Field</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="inlineStr">
+        <is>
+          <t>Fill pre-op instructions or notes field</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F144" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G144" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" s="9" t="inlineStr">
+        <is>
+          <t>19:45:23</t>
+        </is>
+      </c>
+      <c r="I144" s="10" t="inlineStr"/>
+    </row>
+    <row r="145" ht="22" customHeight="1">
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>APPT-010</t>
+        </is>
+      </c>
+      <c r="B145" s="10" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>Submit Schedule Appointment Form</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>Click Save / Schedule appointment button</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F145" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G145" s="9" t="n">
+        <v>3.011</v>
+      </c>
+      <c r="H145" s="9" t="inlineStr">
+        <is>
+          <t>19:45:23</t>
+        </is>
+      </c>
+      <c r="I145" s="10" t="inlineStr"/>
+    </row>
+    <row r="146" ht="22" customHeight="1">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>APPT-011</t>
+        </is>
+      </c>
+      <c r="B146" s="10" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
+        <is>
+          <t>Verify Scheduled Appointment in List</t>
+        </is>
+      </c>
+      <c r="D146" s="10" t="inlineStr">
+        <is>
+          <t>Ensure newly scheduled appointment appears in list view</t>
+        </is>
+      </c>
+      <c r="E146" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F146" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G146" s="9" t="n">
+        <v>6.046</v>
+      </c>
+      <c r="H146" s="9" t="inlineStr">
+        <is>
+          <t>19:45:26</t>
+        </is>
+      </c>
+      <c r="I146" s="10" t="inlineStr"/>
+    </row>
+    <row r="147" ht="22" customHeight="1">
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>APPT-012</t>
+        </is>
+      </c>
+      <c r="B147" s="10" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C147" s="10" t="inlineStr">
+        <is>
+          <t>Filter Appointments by Status: Upcoming</t>
+        </is>
+      </c>
+      <c r="D147" s="10" t="inlineStr">
+        <is>
+          <t>Filter schedule to show upcoming appointments only</t>
+        </is>
+      </c>
+      <c r="E147" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F147" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G147" s="9" t="n">
+        <v>3.025</v>
+      </c>
+      <c r="H147" s="9" t="inlineStr">
+        <is>
+          <t>19:45:32</t>
+        </is>
+      </c>
+      <c r="I147" s="10" t="inlineStr"/>
+    </row>
+    <row r="148" ht="22" customHeight="1">
+      <c r="A148" s="9" t="inlineStr">
+        <is>
+          <t>APPT-013</t>
+        </is>
+      </c>
+      <c r="B148" s="10" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>Filter Appointments by Status: Completed</t>
+        </is>
+      </c>
+      <c r="D148" s="10" t="inlineStr">
+        <is>
+          <t>Filter schedule to show completed appointments</t>
+        </is>
+      </c>
+      <c r="E148" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F148" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G148" s="9" t="n">
+        <v>3.027</v>
+      </c>
+      <c r="H148" s="9" t="inlineStr">
+        <is>
+          <t>19:45:35</t>
+        </is>
+      </c>
+      <c r="I148" s="10" t="inlineStr"/>
+    </row>
+    <row r="149" ht="22" customHeight="1">
+      <c r="A149" s="9" t="inlineStr">
+        <is>
+          <t>APPT-014</t>
+        </is>
+      </c>
+      <c r="B149" s="10" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
+        <is>
+          <t>Reschedule Appointment Action Trigger</t>
+        </is>
+      </c>
+      <c r="D149" s="10" t="inlineStr">
+        <is>
+          <t>Click appointment edit/reschedule option</t>
+        </is>
+      </c>
+      <c r="E149" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F149" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G149" s="9" t="n">
+        <v>6.104</v>
+      </c>
+      <c r="H149" s="9" t="inlineStr">
+        <is>
+          <t>19:45:38</t>
+        </is>
+      </c>
+      <c r="I149" s="10" t="inlineStr"/>
+    </row>
+    <row r="150" ht="22" customHeight="1">
+      <c r="A150" s="9" t="inlineStr">
+        <is>
+          <t>APPT-015</t>
+        </is>
+      </c>
+      <c r="B150" s="10" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C150" s="10" t="inlineStr">
+        <is>
+          <t>Close Appointment Modal Dialog</t>
+        </is>
+      </c>
+      <c r="D150" s="10" t="inlineStr">
+        <is>
+          <t>Dismiss schedule modal dialog</t>
+        </is>
+      </c>
+      <c r="E150" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F150" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G150" s="9" t="n">
+        <v>3.252</v>
+      </c>
+      <c r="H150" s="9" t="inlineStr">
+        <is>
+          <t>19:45:44</t>
+        </is>
+      </c>
+      <c r="I150" s="10" t="inlineStr"/>
+    </row>
+    <row r="151" ht="22" customHeight="1">
+      <c r="A151" s="9" t="inlineStr">
+        <is>
+          <t>SETT-001</t>
+        </is>
+      </c>
+      <c r="B151" s="10" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C151" s="10" t="inlineStr">
+        <is>
+          <t>Navigate to Settings Screen</t>
+        </is>
+      </c>
+      <c r="D151" s="10" t="inlineStr">
+        <is>
+          <t>Open Settings page and verify options</t>
+        </is>
+      </c>
+      <c r="E151" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F151" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G151" s="9" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="H151" s="9" t="inlineStr">
+        <is>
+          <t>19:45:51</t>
+        </is>
+      </c>
+      <c r="I151" s="10" t="inlineStr"/>
+    </row>
+    <row r="152" ht="22" customHeight="1">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>SETT-002</t>
+        </is>
+      </c>
+      <c r="B152" s="10" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
+        <is>
+          <t>Change Default Tooth Numbering System to FDI</t>
+        </is>
+      </c>
+      <c r="D152" s="10" t="inlineStr">
+        <is>
+          <t>Change numbering system select option to FDI standard</t>
+        </is>
+      </c>
+      <c r="E152" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F152" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G152" s="9" t="n">
+        <v>3.039</v>
+      </c>
+      <c r="H152" s="9" t="inlineStr">
+        <is>
+          <t>19:45:54</t>
+        </is>
+      </c>
+      <c r="I152" s="10" t="inlineStr"/>
+    </row>
+    <row r="153" ht="22" customHeight="1">
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>SETT-003</t>
+        </is>
+      </c>
+      <c r="B153" s="10" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C153" s="10" t="inlineStr">
+        <is>
+          <t>Change Default Tooth Numbering System to Universal</t>
+        </is>
+      </c>
+      <c r="D153" s="10" t="inlineStr">
+        <is>
+          <t>Change numbering system select option to Universal (1-32)</t>
+        </is>
+      </c>
+      <c r="E153" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F153" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G153" s="9" t="n">
+        <v>3.052</v>
+      </c>
+      <c r="H153" s="9" t="inlineStr">
+        <is>
+          <t>19:45:57</t>
+        </is>
+      </c>
+      <c r="I153" s="10" t="inlineStr"/>
+    </row>
+    <row r="154" ht="22" customHeight="1">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>SETT-004</t>
+        </is>
+      </c>
+      <c r="B154" s="10" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C154" s="10" t="inlineStr">
+        <is>
+          <t>Update Doctor Profile Name Field</t>
+        </is>
+      </c>
+      <c r="D154" s="10" t="inlineStr">
+        <is>
+          <t>Verify editable practitioner full name input</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F154" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G154" s="9" t="n">
+        <v>6.058</v>
+      </c>
+      <c r="H154" s="9" t="inlineStr">
+        <is>
+          <t>19:46:00</t>
+        </is>
+      </c>
+      <c r="I154" s="10" t="inlineStr"/>
+    </row>
+    <row r="155" ht="22" customHeight="1">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>SETT-005</t>
+        </is>
+      </c>
+      <c r="B155" s="10" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C155" s="10" t="inlineStr">
+        <is>
+          <t>Update Dental License Number Field</t>
+        </is>
+      </c>
+      <c r="D155" s="10" t="inlineStr">
+        <is>
+          <t>Verify editable dental license registration ID field</t>
+        </is>
+      </c>
+      <c r="E155" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F155" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G155" s="9" t="n">
+        <v>3.034</v>
+      </c>
+      <c r="H155" s="9" t="inlineStr">
+        <is>
+          <t>19:46:06</t>
+        </is>
+      </c>
+      <c r="I155" s="10" t="inlineStr"/>
+    </row>
+    <row r="156" ht="22" customHeight="1">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
+          <t>SETT-006</t>
+        </is>
+      </c>
+      <c r="B156" s="10" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>Update Clinic Title Banner Text</t>
+        </is>
+      </c>
+      <c r="D156" s="10" t="inlineStr">
+        <is>
+          <t>Verify editable clinical practice title</t>
+        </is>
+      </c>
+      <c r="E156" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F156" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G156" s="9" t="n">
+        <v>6.061</v>
+      </c>
+      <c r="H156" s="9" t="inlineStr">
+        <is>
+          <t>19:46:09</t>
+        </is>
+      </c>
+      <c r="I156" s="10" t="inlineStr"/>
+    </row>
+    <row r="157" ht="22" customHeight="1">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t>SETT-007</t>
+        </is>
+      </c>
+      <c r="B157" s="10" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
+        <is>
+          <t>Toggle Dark Mode Theme Switcher from Settings</t>
+        </is>
+      </c>
+      <c r="D157" s="10" t="inlineStr">
+        <is>
+          <t>Click theme toggle switch inside settings panel</t>
+        </is>
+      </c>
+      <c r="E157" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F157" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G157" s="9" t="n">
+        <v>6.085</v>
+      </c>
+      <c r="H157" s="9" t="inlineStr">
+        <is>
+          <t>19:46:15</t>
+        </is>
+      </c>
+      <c r="I157" s="10" t="inlineStr"/>
+    </row>
+    <row r="158" ht="22" customHeight="1">
+      <c r="A158" s="9" t="inlineStr">
+        <is>
+          <t>SETT-008</t>
+        </is>
+      </c>
+      <c r="B158" s="10" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C158" s="10" t="inlineStr">
+        <is>
+          <t>Clear Local Application Cache Button</t>
+        </is>
+      </c>
+      <c r="D158" s="10" t="inlineStr">
+        <is>
+          <t>Test clear local application storage cache trigger</t>
+        </is>
+      </c>
+      <c r="E158" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F158" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G158" s="9" t="n">
+        <v>6.075</v>
+      </c>
+      <c r="H158" s="9" t="inlineStr">
+        <is>
+          <t>19:46:21</t>
+        </is>
+      </c>
+      <c r="I158" s="10" t="inlineStr"/>
+    </row>
+    <row r="159" ht="22" customHeight="1">
+      <c r="A159" s="9" t="inlineStr">
+        <is>
+          <t>SETT-009</t>
+        </is>
+      </c>
+      <c r="B159" s="10" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
+        <is>
+          <t>Export Local Database Backup JSON</t>
+        </is>
+      </c>
+      <c r="D159" s="10" t="inlineStr">
+        <is>
+          <t>Click Backup / Export DB button to generate backup file</t>
+        </is>
+      </c>
+      <c r="E159" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F159" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G159" s="9" t="n">
+        <v>6.099</v>
+      </c>
+      <c r="H159" s="9" t="inlineStr">
+        <is>
+          <t>19:46:27</t>
+        </is>
+      </c>
+      <c r="I159" s="10" t="inlineStr"/>
+    </row>
+    <row r="160" ht="22" customHeight="1">
+      <c r="A160" s="9" t="inlineStr">
+        <is>
+          <t>SETT-010</t>
+        </is>
+      </c>
+      <c r="B160" s="10" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
+        <is>
+          <t>Import Database Backup JSON File</t>
+        </is>
+      </c>
+      <c r="D160" s="10" t="inlineStr">
+        <is>
+          <t>Verify file upload picker for database import</t>
+        </is>
+      </c>
+      <c r="E160" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F160" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G160" s="9" t="n">
+        <v>3.039</v>
+      </c>
+      <c r="H160" s="9" t="inlineStr">
+        <is>
+          <t>19:46:33</t>
+        </is>
+      </c>
+      <c r="I160" s="10" t="inlineStr"/>
+    </row>
+    <row r="161" ht="22" customHeight="1">
+      <c r="A161" s="9" t="inlineStr">
+        <is>
+          <t>SETT-011</t>
+        </is>
+      </c>
+      <c r="B161" s="10" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
+        <is>
+          <t>Verify Local Storage DB Status Indicator</t>
+        </is>
+      </c>
+      <c r="D161" s="10" t="inlineStr">
+        <is>
+          <t>Check local IndexedDB / Storage health status message</t>
+        </is>
+      </c>
+      <c r="E161" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F161" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G161" s="9" t="n">
+        <v>9.115</v>
+      </c>
+      <c r="H161" s="9" t="inlineStr">
+        <is>
+          <t>19:46:36</t>
+        </is>
+      </c>
+      <c r="I161" s="10" t="inlineStr"/>
+    </row>
+    <row r="162" ht="22" customHeight="1">
+      <c r="A162" s="9" t="inlineStr">
+        <is>
+          <t>SETT-012</t>
+        </is>
+      </c>
+      <c r="B162" s="10" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C162" s="10" t="inlineStr">
+        <is>
+          <t>Save System Preferences Button</t>
+        </is>
+      </c>
+      <c r="D162" s="10" t="inlineStr">
+        <is>
+          <t>Click Save Preferences button</t>
+        </is>
+      </c>
+      <c r="E162" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F162" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G162" s="9" t="n">
+        <v>3.052</v>
+      </c>
+      <c r="H162" s="9" t="inlineStr">
+        <is>
+          <t>19:46:45</t>
+        </is>
+      </c>
+      <c r="I162" s="10" t="inlineStr"/>
+    </row>
+    <row r="163" ht="22" customHeight="1">
+      <c r="A163" s="9" t="inlineStr">
+        <is>
+          <t>SETT-013</t>
+        </is>
+      </c>
+      <c r="B163" s="10" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
+        <is>
+          <t>Reset Preferences to Default Values</t>
+        </is>
+      </c>
+      <c r="D163" s="10" t="inlineStr">
+        <is>
+          <t>Click reset defaults button</t>
+        </is>
+      </c>
+      <c r="E163" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F163" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G163" s="9" t="n">
+        <v>3.003</v>
+      </c>
+      <c r="H163" s="9" t="inlineStr">
+        <is>
+          <t>19:46:48</t>
+        </is>
+      </c>
+      <c r="I163" s="10" t="inlineStr"/>
+    </row>
+    <row r="164" ht="22" customHeight="1">
+      <c r="A164" s="9" t="inlineStr">
+        <is>
+          <t>SETT-014</t>
+        </is>
+      </c>
+      <c r="B164" s="10" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C164" s="10" t="inlineStr">
+        <is>
+          <t>Verify App Build Version Information</t>
+        </is>
+      </c>
+      <c r="D164" s="10" t="inlineStr">
+        <is>
+          <t>Check software version label (v1.0.0 / EndoPredict AI)</t>
+        </is>
+      </c>
+      <c r="E164" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F164" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G164" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H164" s="9" t="inlineStr">
+        <is>
+          <t>19:46:51</t>
+        </is>
+      </c>
+      <c r="I164" s="10" t="inlineStr"/>
+    </row>
+    <row r="165" ht="22" customHeight="1">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>SETT-015</t>
+        </is>
+      </c>
+      <c r="B165" s="10" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C165" s="10" t="inlineStr">
+        <is>
+          <t>License Expiry &amp; Subscription Status Banner</t>
+        </is>
+      </c>
+      <c r="D165" s="10" t="inlineStr">
+        <is>
+          <t>Check practice subscription license active banner</t>
+        </is>
+      </c>
+      <c r="E165" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F165" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G165" s="9" t="n">
+        <v>6.079</v>
+      </c>
+      <c r="H165" s="9" t="inlineStr">
+        <is>
+          <t>19:46:51</t>
+        </is>
+      </c>
+      <c r="I165" s="10" t="inlineStr"/>
+    </row>
+    <row r="166" ht="22" customHeight="1">
+      <c r="A166" s="9" t="inlineStr">
+        <is>
+          <t>AUTH-001</t>
+        </is>
+      </c>
+      <c r="B166" s="10" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C166" s="10" t="inlineStr">
+        <is>
+          <t>Open User Profile / Doctor Settings</t>
+        </is>
+      </c>
+      <c r="D166" s="10" t="inlineStr">
+        <is>
+          <t>Verify Doctor Clinical Profile settings panel</t>
+        </is>
+      </c>
+      <c r="E166" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F166" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G166" s="9" t="n">
+        <v>6.049</v>
+      </c>
+      <c r="H166" s="9" t="inlineStr">
+        <is>
+          <t>19:46:58</t>
+        </is>
+      </c>
+      <c r="I166" s="10" t="inlineStr"/>
+    </row>
+    <row r="167" ht="22" customHeight="1">
+      <c r="A167" s="9" t="inlineStr">
+        <is>
+          <t>AUTH-002</t>
+        </is>
+      </c>
+      <c r="B167" s="10" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C167" s="10" t="inlineStr">
+        <is>
+          <t>Verify Doctor Credentials in Profile Card</t>
+        </is>
+      </c>
+      <c r="D167" s="10" t="inlineStr">
+        <is>
+          <t>Verify profile card displays practitioner credentials</t>
+        </is>
+      </c>
+      <c r="E167" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F167" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G167" s="9" t="n">
+        <v>6.079</v>
+      </c>
+      <c r="H167" s="9" t="inlineStr">
+        <is>
+          <t>19:47:04</t>
+        </is>
+      </c>
+      <c r="I167" s="10" t="inlineStr"/>
+    </row>
+    <row r="168" ht="22" customHeight="1">
+      <c r="A168" s="9" t="inlineStr">
+        <is>
+          <t>AUTH-003</t>
+        </is>
+      </c>
+      <c r="B168" s="10" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C168" s="10" t="inlineStr">
+        <is>
+          <t>Verify Specialization Badge Display</t>
+        </is>
+      </c>
+      <c r="D168" s="10" t="inlineStr">
+        <is>
+          <t>Ensure Endodontic Specialist badge displays</t>
+        </is>
+      </c>
+      <c r="E168" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F168" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G168" s="9" t="n">
+        <v>6.046</v>
+      </c>
+      <c r="H168" s="9" t="inlineStr">
+        <is>
+          <t>19:47:10</t>
+        </is>
+      </c>
+      <c r="I168" s="10" t="inlineStr"/>
+    </row>
+    <row r="169" ht="22" customHeight="1">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>AUTH-004</t>
+        </is>
+      </c>
+      <c r="B169" s="10" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C169" s="10" t="inlineStr">
+        <is>
+          <t>Test Logout Action</t>
+        </is>
+      </c>
+      <c r="D169" s="10" t="inlineStr">
+        <is>
+          <t>Click Logout button to exit session</t>
+        </is>
+      </c>
+      <c r="E169" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F169" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G169" s="9" t="n">
+        <v>3.015</v>
+      </c>
+      <c r="H169" s="9" t="inlineStr">
+        <is>
+          <t>19:47:16</t>
+        </is>
+      </c>
+      <c r="I169" s="10" t="inlineStr"/>
+    </row>
+    <row r="170" ht="22" customHeight="1">
+      <c r="A170" s="9" t="inlineStr">
+        <is>
+          <t>AUTH-005</t>
+        </is>
+      </c>
+      <c r="B170" s="10" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C170" s="10" t="inlineStr">
+        <is>
+          <t>Verify Doctor Login Screen Render</t>
+        </is>
+      </c>
+      <c r="D170" s="10" t="inlineStr">
+        <is>
+          <t>Verify Login email &amp; password form display</t>
+        </is>
+      </c>
+      <c r="E170" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F170" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G170" s="9" t="n">
+        <v>6.064</v>
+      </c>
+      <c r="H170" s="9" t="inlineStr">
+        <is>
+          <t>19:47:19</t>
+        </is>
+      </c>
+      <c r="I170" s="10" t="inlineStr"/>
+    </row>
+    <row r="171" ht="22" customHeight="1">
+      <c r="A171" s="9" t="inlineStr">
+        <is>
+          <t>AUTH-006</t>
+        </is>
+      </c>
+      <c r="B171" s="10" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>Login Form - Email Input Field</t>
+        </is>
+      </c>
+      <c r="D171" s="10" t="inlineStr">
+        <is>
+          <t>Verify email input field on login screen</t>
+        </is>
+      </c>
+      <c r="E171" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F171" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G171" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" s="9" t="inlineStr">
+        <is>
+          <t>19:47:25</t>
+        </is>
+      </c>
+      <c r="I171" s="10" t="inlineStr"/>
+    </row>
+    <row r="172" ht="22" customHeight="1">
+      <c r="A172" s="9" t="inlineStr">
+        <is>
+          <t>AUTH-007</t>
+        </is>
+      </c>
+      <c r="B172" s="10" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C172" s="10" t="inlineStr">
+        <is>
+          <t>Login Form - Password Input Field</t>
+        </is>
+      </c>
+      <c r="D172" s="10" t="inlineStr">
+        <is>
+          <t>Verify password input field on login screen</t>
+        </is>
+      </c>
+      <c r="E172" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F172" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G172" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" s="9" t="inlineStr">
+        <is>
+          <t>19:47:25</t>
+        </is>
+      </c>
+      <c r="I172" s="10" t="inlineStr"/>
+    </row>
+    <row r="173" ht="22" customHeight="1">
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>AUTH-008</t>
+        </is>
+      </c>
+      <c r="B173" s="10" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C173" s="10" t="inlineStr">
+        <is>
+          <t>Login Form - Show/Hide Password Toggle</t>
+        </is>
+      </c>
+      <c r="D173" s="10" t="inlineStr">
+        <is>
+          <t>Toggle password visibility eye icon</t>
+        </is>
+      </c>
+      <c r="E173" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F173" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G173" s="9" t="n">
+        <v>3.045</v>
+      </c>
+      <c r="H173" s="9" t="inlineStr">
+        <is>
+          <t>19:47:25</t>
+        </is>
+      </c>
+      <c r="I173" s="10" t="inlineStr"/>
+    </row>
+    <row r="174" ht="22" customHeight="1">
+      <c r="A174" s="9" t="inlineStr">
+        <is>
+          <t>AUTH-009</t>
+        </is>
+      </c>
+      <c r="B174" s="10" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C174" s="10" t="inlineStr">
+        <is>
+          <t>Test Demo Doctor Credentials Trigger</t>
+        </is>
+      </c>
+      <c r="D174" s="10" t="inlineStr">
+        <is>
+          <t>Click 'Use Demo Doctor Account' button</t>
+        </is>
+      </c>
+      <c r="E174" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F174" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G174" s="9" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="H174" s="9" t="inlineStr">
+        <is>
+          <t>19:47:28</t>
+        </is>
+      </c>
+      <c r="I174" s="10" t="inlineStr"/>
+    </row>
+    <row r="175" ht="22" customHeight="1">
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>AUTH-010</t>
+        </is>
+      </c>
+      <c r="B175" s="10" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C175" s="10" t="inlineStr">
+        <is>
+          <t>Test Doctor Login Submit Flow</t>
+        </is>
+      </c>
+      <c r="D175" s="10" t="inlineStr">
+        <is>
+          <t>Submit doctor login form to restore session</t>
+        </is>
+      </c>
+      <c r="E175" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F175" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G175" s="9" t="n">
+        <v>4.027</v>
+      </c>
+      <c r="H175" s="9" t="inlineStr">
+        <is>
+          <t>19:47:31</t>
+        </is>
+      </c>
+      <c r="I175" s="10" t="inlineStr"/>
+    </row>
+    <row r="176" ht="22" customHeight="1">
+      <c r="A176" s="9" t="inlineStr">
+        <is>
+          <t>AUTH-011</t>
+        </is>
+      </c>
+      <c r="B176" s="10" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C176" s="10" t="inlineStr">
+        <is>
+          <t>Switch to Patient Portal Mode</t>
+        </is>
+      </c>
+      <c r="D176" s="10" t="inlineStr">
+        <is>
+          <t>Test Patient Portal mode switch link</t>
+        </is>
+      </c>
+      <c r="E176" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F176" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G176" s="9" t="n">
+        <v>3.038</v>
+      </c>
+      <c r="H176" s="9" t="inlineStr">
+        <is>
+          <t>19:47:35</t>
+        </is>
+      </c>
+      <c r="I176" s="10" t="inlineStr"/>
+    </row>
+    <row r="177" ht="22" customHeight="1">
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>AUTH-012</t>
+        </is>
+      </c>
+      <c r="B177" s="10" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C177" s="10" t="inlineStr">
+        <is>
+          <t>Return to Doctor Clinical Portal View</t>
+        </is>
+      </c>
+      <c r="D177" s="10" t="inlineStr">
+        <is>
+          <t>Switch back from patient portal mode to doctor portal</t>
+        </is>
+      </c>
+      <c r="E177" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F177" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G177" s="9" t="n">
+        <v>3.009</v>
+      </c>
+      <c r="H177" s="9" t="inlineStr">
+        <is>
+          <t>19:47:38</t>
+        </is>
+      </c>
+      <c r="I177" s="10" t="inlineStr"/>
+    </row>
+    <row r="178" ht="22" customHeight="1">
+      <c r="A178" s="9" t="inlineStr">
+        <is>
+          <t>NOTIF-001</t>
+        </is>
+      </c>
+      <c r="B178" s="10" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C178" s="10" t="inlineStr">
+        <is>
+          <t>Open Notifications Dropdown</t>
+        </is>
+      </c>
+      <c r="D178" s="10" t="inlineStr">
+        <is>
+          <t>Click header bell icon to open notifications popover</t>
+        </is>
+      </c>
+      <c r="E178" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F178" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G178" s="9" t="n">
+        <v>6.099</v>
+      </c>
+      <c r="H178" s="9" t="inlineStr">
+        <is>
+          <t>19:47:41</t>
+        </is>
+      </c>
+      <c r="I178" s="10" t="inlineStr"/>
+    </row>
+    <row r="179" ht="22" customHeight="1">
+      <c r="A179" s="9" t="inlineStr">
+        <is>
+          <t>NOTIF-002</t>
+        </is>
+      </c>
+      <c r="B179" s="10" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C179" s="10" t="inlineStr">
+        <is>
+          <t>Verify Notifications Popover Render</t>
+        </is>
+      </c>
+      <c r="D179" s="10" t="inlineStr">
+        <is>
+          <t>Ensure notifications menu dropdown renders</t>
+        </is>
+      </c>
+      <c r="E179" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F179" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G179" s="9" t="n">
+        <v>3.028</v>
+      </c>
+      <c r="H179" s="9" t="inlineStr">
+        <is>
+          <t>19:47:47</t>
+        </is>
+      </c>
+      <c r="I179" s="10" t="inlineStr"/>
+    </row>
+    <row r="180" ht="22" customHeight="1">
+      <c r="A180" s="9" t="inlineStr">
+        <is>
+          <t>NOTIF-003</t>
+        </is>
+      </c>
+      <c r="B180" s="10" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C180" s="10" t="inlineStr">
+        <is>
+          <t>Verify Unread Notification Count Badge</t>
+        </is>
+      </c>
+      <c r="D180" s="10" t="inlineStr">
+        <is>
+          <t>Check numerical unread alert badge overlay</t>
+        </is>
+      </c>
+      <c r="E180" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F180" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G180" s="9" t="n">
+        <v>3.013</v>
+      </c>
+      <c r="H180" s="9" t="inlineStr">
+        <is>
+          <t>19:47:50</t>
+        </is>
+      </c>
+      <c r="I180" s="10" t="inlineStr"/>
+    </row>
+    <row r="181" ht="22" customHeight="1">
+      <c r="A181" s="9" t="inlineStr">
+        <is>
+          <t>NOTIF-004</t>
+        </is>
+      </c>
+      <c r="B181" s="10" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C181" s="10" t="inlineStr">
+        <is>
+          <t>Click Individual Notification Alert Item</t>
+        </is>
+      </c>
+      <c r="D181" s="10" t="inlineStr">
+        <is>
+          <t>Click notification item to navigate to clinical case</t>
+        </is>
+      </c>
+      <c r="E181" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F181" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G181" s="9" t="n">
+        <v>6.055</v>
+      </c>
+      <c r="H181" s="9" t="inlineStr">
+        <is>
+          <t>19:47:53</t>
+        </is>
+      </c>
+      <c r="I181" s="10" t="inlineStr"/>
+    </row>
+    <row r="182" ht="22" customHeight="1">
+      <c r="A182" s="9" t="inlineStr">
+        <is>
+          <t>NOTIF-005</t>
+        </is>
+      </c>
+      <c r="B182" s="10" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C182" s="10" t="inlineStr">
+        <is>
+          <t>Click Mark All as Read Button</t>
+        </is>
+      </c>
+      <c r="D182" s="10" t="inlineStr">
+        <is>
+          <t>Clear unread notification count badge</t>
+        </is>
+      </c>
+      <c r="E182" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F182" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G182" s="9" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="H182" s="9" t="inlineStr">
+        <is>
+          <t>19:47:59</t>
+        </is>
+      </c>
+      <c r="I182" s="10" t="inlineStr"/>
+    </row>
+    <row r="183" ht="22" customHeight="1">
+      <c r="A183" s="9" t="inlineStr">
+        <is>
+          <t>NOTIF-006</t>
+        </is>
+      </c>
+      <c r="B183" s="10" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C183" s="10" t="inlineStr">
+        <is>
+          <t>Clear Notification List</t>
+        </is>
+      </c>
+      <c r="D183" s="10" t="inlineStr">
+        <is>
+          <t>Clear all notifications from list</t>
+        </is>
+      </c>
+      <c r="E183" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F183" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G183" s="9" t="n">
+        <v>3.013</v>
+      </c>
+      <c r="H183" s="9" t="inlineStr">
+        <is>
+          <t>19:48:02</t>
+        </is>
+      </c>
+      <c r="I183" s="10" t="inlineStr"/>
+    </row>
+    <row r="184" ht="22" customHeight="1">
+      <c r="A184" s="9" t="inlineStr">
+        <is>
+          <t>NOTIF-007</t>
+        </is>
+      </c>
+      <c r="B184" s="10" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C184" s="10" t="inlineStr">
+        <is>
+          <t>System Health Online Status Indicator</t>
+        </is>
+      </c>
+      <c r="D184" s="10" t="inlineStr">
+        <is>
+          <t>Check green online status dot in system header</t>
+        </is>
+      </c>
+      <c r="E184" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F184" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G184" s="9" t="n">
+        <v>3.036</v>
+      </c>
+      <c r="H184" s="9" t="inlineStr">
+        <is>
+          <t>19:48:05</t>
+        </is>
+      </c>
+      <c r="I184" s="10" t="inlineStr"/>
+    </row>
+    <row r="185" ht="22" customHeight="1">
+      <c r="A185" s="9" t="inlineStr">
+        <is>
+          <t>NOTIF-008</t>
+        </is>
+      </c>
+      <c r="B185" s="10" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C185" s="10" t="inlineStr">
+        <is>
+          <t>Practice Location / Clinic Switcher Dropdown</t>
+        </is>
+      </c>
+      <c r="D185" s="10" t="inlineStr">
+        <is>
+          <t>Check clinic location dropdown selector</t>
+        </is>
+      </c>
+      <c r="E185" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F185" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G185" s="9" t="n">
+        <v>6.028</v>
+      </c>
+      <c r="H185" s="9" t="inlineStr">
+        <is>
+          <t>19:48:08</t>
+        </is>
+      </c>
+      <c r="I185" s="10" t="inlineStr"/>
+    </row>
+    <row r="186" ht="22" customHeight="1">
+      <c r="A186" s="9" t="inlineStr">
+        <is>
+          <t>NOTIF-009</t>
+        </is>
+      </c>
+      <c r="B186" s="10" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C186" s="10" t="inlineStr">
+        <is>
+          <t>Quick Search Header Shortcut</t>
+        </is>
+      </c>
+      <c r="D186" s="10" t="inlineStr">
+        <is>
+          <t>Verify global search input field in header</t>
+        </is>
+      </c>
+      <c r="E186" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F186" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G186" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" s="9" t="inlineStr">
+        <is>
+          <t>19:48:14</t>
+        </is>
+      </c>
+      <c r="I186" s="10" t="inlineStr"/>
+    </row>
+    <row r="187" ht="22" customHeight="1">
+      <c r="A187" s="9" t="inlineStr">
+        <is>
+          <t>NOTIF-010</t>
+        </is>
+      </c>
+      <c r="B187" s="10" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C187" s="10" t="inlineStr">
+        <is>
+          <t>Help &amp; Clinical Documentation Link</t>
+        </is>
+      </c>
+      <c r="D187" s="10" t="inlineStr">
+        <is>
+          <t>Click Help documentation link</t>
+        </is>
+      </c>
+      <c r="E187" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F187" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G187" s="9" t="n">
+        <v>6.118</v>
+      </c>
+      <c r="H187" s="9" t="inlineStr">
+        <is>
+          <t>19:48:14</t>
+        </is>
+      </c>
+      <c r="I187" s="10" t="inlineStr"/>
+    </row>
+    <row r="188" ht="22" customHeight="1">
+      <c r="A188" s="9" t="inlineStr">
+        <is>
+          <t>NOTIF-011</t>
+        </is>
+      </c>
+      <c r="B188" s="10" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C188" s="10" t="inlineStr">
+        <is>
+          <t>Keyboard Shortcut Hint Display (Ctrl+K)</t>
+        </is>
+      </c>
+      <c r="D188" s="10" t="inlineStr">
+        <is>
+          <t>Verify search shortcut hint badge display</t>
+        </is>
+      </c>
+      <c r="E188" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F188" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G188" s="9" t="n">
+        <v>6.031</v>
+      </c>
+      <c r="H188" s="9" t="inlineStr">
+        <is>
+          <t>19:48:20</t>
+        </is>
+      </c>
+      <c r="I188" s="10" t="inlineStr"/>
+    </row>
+    <row r="189" ht="22" customHeight="1">
+      <c r="A189" s="9" t="inlineStr">
+        <is>
+          <t>NOTIF-012</t>
+        </is>
+      </c>
+      <c r="B189" s="10" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C189" s="10" t="inlineStr">
+        <is>
+          <t>Close Notification Popover Menu</t>
+        </is>
+      </c>
+      <c r="D189" s="10" t="inlineStr">
+        <is>
+          <t>Dismiss notification menu dropdown</t>
+        </is>
+      </c>
+      <c r="E189" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F189" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G189" s="9" t="n">
+        <v>3.227</v>
+      </c>
+      <c r="H189" s="9" t="inlineStr">
+        <is>
+          <t>19:48:26</t>
+        </is>
+      </c>
+      <c r="I189" s="10" t="inlineStr"/>
+    </row>
+    <row r="190" ht="22" customHeight="1">
+      <c r="A190" s="9" t="inlineStr">
+        <is>
+          <t>UI-001</t>
+        </is>
+      </c>
+      <c r="B190" s="10" t="inlineStr">
+        <is>
+          <t>Theme &amp; Layout</t>
+        </is>
+      </c>
+      <c r="C190" s="10" t="inlineStr">
+        <is>
+          <t>Toggle Dark Mode Theme Switcher</t>
+        </is>
+      </c>
+      <c r="D190" s="10" t="inlineStr">
+        <is>
+          <t>Click Dark/Light theme toggle switch in sidebar</t>
+        </is>
+      </c>
+      <c r="E190" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F190" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G190" s="9" t="n">
+        <v>6.116</v>
+      </c>
+      <c r="H190" s="9" t="inlineStr">
+        <is>
+          <t>19:48:30</t>
+        </is>
+      </c>
+      <c r="I190" s="10" t="inlineStr"/>
+    </row>
+    <row r="191" ht="22" customHeight="1">
+      <c r="A191" s="9" t="inlineStr">
+        <is>
+          <t>UI-002</t>
+        </is>
+      </c>
+      <c r="B191" s="10" t="inlineStr">
+        <is>
+          <t>Theme &amp; Layout</t>
+        </is>
+      </c>
+      <c r="C191" s="10" t="inlineStr">
+        <is>
+          <t>Verify Dark Mode Background Theme Style</t>
+        </is>
+      </c>
+      <c r="D191" s="10" t="inlineStr">
+        <is>
+          <t>Check document body background styling changes</t>
+        </is>
+      </c>
+      <c r="E191" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F191" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G191" s="9" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="H191" s="9" t="inlineStr">
+        <is>
+          <t>19:48:36</t>
+        </is>
+      </c>
+      <c r="I191" s="10" t="inlineStr"/>
+    </row>
+    <row r="192" ht="22" customHeight="1">
+      <c r="A192" s="9" t="inlineStr">
+        <is>
+          <t>UI-003</t>
+        </is>
+      </c>
+      <c r="B192" s="10" t="inlineStr">
+        <is>
+          <t>Theme &amp; Layout</t>
+        </is>
+      </c>
+      <c r="C192" s="10" t="inlineStr">
+        <is>
+          <t>Verify Dark Mode Text Contrast Ratio</t>
+        </is>
+      </c>
+      <c r="D192" s="10" t="inlineStr">
+        <is>
+          <t>Check dark theme typography color contrast</t>
+        </is>
+      </c>
+      <c r="E192" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F192" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G192" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" s="9" t="inlineStr">
+        <is>
+          <t>19:48:36</t>
+        </is>
+      </c>
+      <c r="I192" s="10" t="inlineStr"/>
+    </row>
+    <row r="193" ht="22" customHeight="1">
+      <c r="A193" s="9" t="inlineStr">
+        <is>
+          <t>UI-004</t>
+        </is>
+      </c>
+      <c r="B193" s="10" t="inlineStr">
+        <is>
+          <t>Theme &amp; Layout</t>
+        </is>
+      </c>
+      <c r="C193" s="10" t="inlineStr">
+        <is>
+          <t>Toggle Back to Light Mode Theme</t>
+        </is>
+      </c>
+      <c r="D193" s="10" t="inlineStr">
+        <is>
+          <t>Click theme switch button again to revert to light theme</t>
+        </is>
+      </c>
+      <c r="E193" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F193" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G193" s="9" t="n">
+        <v>6.088</v>
+      </c>
+      <c r="H193" s="9" t="inlineStr">
+        <is>
+          <t>19:48:36</t>
+        </is>
+      </c>
+      <c r="I193" s="10" t="inlineStr"/>
+    </row>
+    <row r="194" ht="22" customHeight="1">
+      <c r="A194" s="9" t="inlineStr">
+        <is>
+          <t>UI-005</t>
+        </is>
+      </c>
+      <c r="B194" s="10" t="inlineStr">
+        <is>
+          <t>Theme &amp; Layout</t>
+        </is>
+      </c>
+      <c r="C194" s="10" t="inlineStr">
+        <is>
+          <t>Mobile Viewport Test (Width 390px)</t>
+        </is>
+      </c>
+      <c r="D194" s="10" t="inlineStr">
+        <is>
+          <t>Resize browser window to mobile iPhone 12 Pro dimensions (390x844)</t>
+        </is>
+      </c>
+      <c r="E194" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F194" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G194" s="9" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="H194" s="9" t="inlineStr">
+        <is>
+          <t>19:48:42</t>
+        </is>
+      </c>
+      <c r="I194" s="10" t="inlineStr"/>
+    </row>
+    <row r="195" ht="22" customHeight="1">
+      <c r="A195" s="9" t="inlineStr">
+        <is>
           <t>UI-006</t>
         </is>
       </c>
-      <c r="B125" s="10" t="inlineStr">
+      <c r="B195" s="10" t="inlineStr">
         <is>
           <t>Theme &amp; Layout</t>
         </is>
       </c>
-      <c r="C125" s="10" t="inlineStr">
+      <c r="C195" s="10" t="inlineStr">
+        <is>
+          <t>Verify Mobile Bottom Navigation Bar</t>
+        </is>
+      </c>
+      <c r="D195" s="10" t="inlineStr">
+        <is>
+          <t>Ensure desktop sidebar hides and bottom mobile nav bar appears</t>
+        </is>
+      </c>
+      <c r="E195" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F195" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G195" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" s="9" t="inlineStr">
+        <is>
+          <t>19:48:43</t>
+        </is>
+      </c>
+      <c r="I195" s="10" t="inlineStr"/>
+    </row>
+    <row r="196" ht="22" customHeight="1">
+      <c r="A196" s="9" t="inlineStr">
+        <is>
+          <t>UI-007</t>
+        </is>
+      </c>
+      <c r="B196" s="10" t="inlineStr">
+        <is>
+          <t>Theme &amp; Layout</t>
+        </is>
+      </c>
+      <c r="C196" s="10" t="inlineStr">
+        <is>
+          <t>Verify Desktop Sidebar Auto-hide on Mobile</t>
+        </is>
+      </c>
+      <c r="D196" s="10" t="inlineStr">
+        <is>
+          <t>Verify navigation drawer collapse on narrow viewports</t>
+        </is>
+      </c>
+      <c r="E196" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F196" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G196" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" s="9" t="inlineStr">
+        <is>
+          <t>19:48:43</t>
+        </is>
+      </c>
+      <c r="I196" s="10" t="inlineStr"/>
+    </row>
+    <row r="197" ht="22" customHeight="1">
+      <c r="A197" s="9" t="inlineStr">
+        <is>
+          <t>UI-008</t>
+        </is>
+      </c>
+      <c r="B197" s="10" t="inlineStr">
+        <is>
+          <t>Theme &amp; Layout</t>
+        </is>
+      </c>
+      <c r="C197" s="10" t="inlineStr">
+        <is>
+          <t>Mobile Hamburger Menu Drawer Toggle</t>
+        </is>
+      </c>
+      <c r="D197" s="10" t="inlineStr">
+        <is>
+          <t>Click mobile hamburger menu button to open drawer</t>
+        </is>
+      </c>
+      <c r="E197" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F197" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" s="9" t="inlineStr">
+        <is>
+          <t>19:48:43</t>
+        </is>
+      </c>
+      <c r="I197" s="10" t="inlineStr"/>
+    </row>
+    <row r="198" ht="22" customHeight="1">
+      <c r="A198" s="9" t="inlineStr">
+        <is>
+          <t>UI-009</t>
+        </is>
+      </c>
+      <c r="B198" s="10" t="inlineStr">
+        <is>
+          <t>Theme &amp; Layout</t>
+        </is>
+      </c>
+      <c r="C198" s="10" t="inlineStr">
+        <is>
+          <t>Tablet Viewport Test (Width 768px)</t>
+        </is>
+      </c>
+      <c r="D198" s="10" t="inlineStr">
+        <is>
+          <t>Resize browser window to iPad tablet resolution (768x1024)</t>
+        </is>
+      </c>
+      <c r="E198" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F198" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G198" s="9" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="H198" s="9" t="inlineStr">
+        <is>
+          <t>19:48:43</t>
+        </is>
+      </c>
+      <c r="I198" s="10" t="inlineStr"/>
+    </row>
+    <row r="199" ht="22" customHeight="1">
+      <c r="A199" s="9" t="inlineStr">
+        <is>
+          <t>UI-010</t>
+        </is>
+      </c>
+      <c r="B199" s="10" t="inlineStr">
+        <is>
+          <t>Theme &amp; Layout</t>
+        </is>
+      </c>
+      <c r="C199" s="10" t="inlineStr">
+        <is>
+          <t>Verify Tablet Grid Layout Adjustment</t>
+        </is>
+      </c>
+      <c r="D199" s="10" t="inlineStr">
+        <is>
+          <t>Ensure stat cards collapse into 2-column grid layout</t>
+        </is>
+      </c>
+      <c r="E199" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F199" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G199" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" s="9" t="inlineStr">
+        <is>
+          <t>19:48:44</t>
+        </is>
+      </c>
+      <c r="I199" s="10" t="inlineStr"/>
+    </row>
+    <row r="200" ht="22" customHeight="1">
+      <c r="A200" s="9" t="inlineStr">
+        <is>
+          <t>UI-011</t>
+        </is>
+      </c>
+      <c r="B200" s="10" t="inlineStr">
+        <is>
+          <t>Theme &amp; Layout</t>
+        </is>
+      </c>
+      <c r="C200" s="10" t="inlineStr">
         <is>
           <t>Restore Desktop Viewport (Width 1440px)</t>
         </is>
       </c>
-      <c r="D125" s="10" t="inlineStr">
+      <c r="D200" s="10" t="inlineStr">
         <is>
           <t>Restore browser window size back to standard desktop (1440x900)</t>
         </is>
       </c>
-      <c r="E125" s="9" t="inlineStr">
-        <is>
-          <t>Live Chrome</t>
-        </is>
-      </c>
-      <c r="F125" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G125" s="9" t="n">
-        <v>0.856</v>
-      </c>
-      <c r="H125" s="9" t="inlineStr">
-        <is>
-          <t>15:37:43</t>
-        </is>
-      </c>
-      <c r="I125" s="10" t="inlineStr"/>
+      <c r="E200" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F200" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G200" s="9" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="H200" s="9" t="inlineStr">
+        <is>
+          <t>19:48:44</t>
+        </is>
+      </c>
+      <c r="I200" s="10" t="inlineStr"/>
+    </row>
+    <row r="201" ht="22" customHeight="1">
+      <c r="A201" s="9" t="inlineStr">
+        <is>
+          <t>UI-012</t>
+        </is>
+      </c>
+      <c r="B201" s="10" t="inlineStr">
+        <is>
+          <t>Theme &amp; Layout</t>
+        </is>
+      </c>
+      <c r="C201" s="10" t="inlineStr">
+        <is>
+          <t>High-DPI Retina Display Scaling Test</t>
+        </is>
+      </c>
+      <c r="D201" s="10" t="inlineStr">
+        <is>
+          <t>Check crisp rendering of SVG graphics under 2x scaling</t>
+        </is>
+      </c>
+      <c r="E201" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F201" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G201" s="9" t="n">
+        <v>3.064</v>
+      </c>
+      <c r="H201" s="9" t="inlineStr">
+        <is>
+          <t>19:48:45</t>
+        </is>
+      </c>
+      <c r="I201" s="10" t="inlineStr"/>
+    </row>
+    <row r="202" ht="22" customHeight="1">
+      <c r="A202" s="9" t="inlineStr">
+        <is>
+          <t>KEY-001</t>
+        </is>
+      </c>
+      <c r="B202" s="10" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C202" s="10" t="inlineStr">
+        <is>
+          <t>Focus Outline Styling Check</t>
+        </is>
+      </c>
+      <c r="D202" s="10" t="inlineStr">
+        <is>
+          <t>Ensure interactive elements receive visible focus outline</t>
+        </is>
+      </c>
+      <c r="E202" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F202" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G202" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" s="9" t="inlineStr">
+        <is>
+          <t>19:48:48</t>
+        </is>
+      </c>
+      <c r="I202" s="10" t="inlineStr"/>
+    </row>
+    <row r="203" ht="22" customHeight="1">
+      <c r="A203" s="9" t="inlineStr">
+        <is>
+          <t>KEY-002</t>
+        </is>
+      </c>
+      <c r="B203" s="10" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C203" s="10" t="inlineStr">
+        <is>
+          <t>Escape Key Dismisses Active Modals</t>
+        </is>
+      </c>
+      <c r="D203" s="10" t="inlineStr">
+        <is>
+          <t>Send ESC key press to dismiss dialog overlays</t>
+        </is>
+      </c>
+      <c r="E203" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F203" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G203" s="9" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="H203" s="9" t="inlineStr">
+        <is>
+          <t>19:48:48</t>
+        </is>
+      </c>
+      <c r="I203" s="10" t="inlineStr"/>
+    </row>
+    <row r="204" ht="22" customHeight="1">
+      <c r="A204" s="9" t="inlineStr">
+        <is>
+          <t>KEY-003</t>
+        </is>
+      </c>
+      <c r="B204" s="10" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C204" s="10" t="inlineStr">
+        <is>
+          <t>Enter Key Form Submission</t>
+        </is>
+      </c>
+      <c r="D204" s="10" t="inlineStr">
+        <is>
+          <t>Send Enter key in focused input field</t>
+        </is>
+      </c>
+      <c r="E204" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F204" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G204" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" s="9" t="inlineStr">
+        <is>
+          <t>19:48:48</t>
+        </is>
+      </c>
+      <c r="I204" s="10" t="inlineStr"/>
+    </row>
+    <row r="205" ht="22" customHeight="1">
+      <c r="A205" s="9" t="inlineStr">
+        <is>
+          <t>KEY-004</t>
+        </is>
+      </c>
+      <c r="B205" s="10" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C205" s="10" t="inlineStr">
+        <is>
+          <t>Tab Key Element Traversal Cycle</t>
+        </is>
+      </c>
+      <c r="D205" s="10" t="inlineStr">
+        <is>
+          <t>Send Tab key to iterate through interactive controls</t>
+        </is>
+      </c>
+      <c r="E205" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F205" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G205" s="9" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="H205" s="9" t="inlineStr">
+        <is>
+          <t>19:48:48</t>
+        </is>
+      </c>
+      <c r="I205" s="10" t="inlineStr"/>
+    </row>
+    <row r="206" ht="22" customHeight="1">
+      <c r="A206" s="9" t="inlineStr">
+        <is>
+          <t>KEY-005</t>
+        </is>
+      </c>
+      <c r="B206" s="10" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C206" s="10" t="inlineStr">
+        <is>
+          <t>Arrow Key Traversal in Dropdowns</t>
+        </is>
+      </c>
+      <c r="D206" s="10" t="inlineStr">
+        <is>
+          <t>Verify arrow key navigation within select elements</t>
+        </is>
+      </c>
+      <c r="E206" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F206" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G206" s="9" t="n">
+        <v>3.043</v>
+      </c>
+      <c r="H206" s="9" t="inlineStr">
+        <is>
+          <t>19:48:48</t>
+        </is>
+      </c>
+      <c r="I206" s="10" t="inlineStr"/>
+    </row>
+    <row r="207" ht="22" customHeight="1">
+      <c r="A207" s="9" t="inlineStr">
+        <is>
+          <t>KEY-006</t>
+        </is>
+      </c>
+      <c r="B207" s="10" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C207" s="10" t="inlineStr">
+        <is>
+          <t>Page Down Keyboard Scroll</t>
+        </is>
+      </c>
+      <c r="D207" s="10" t="inlineStr">
+        <is>
+          <t>Send Page Down key press to scroll view</t>
+        </is>
+      </c>
+      <c r="E207" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F207" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G207" s="9" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H207" s="9" t="inlineStr">
+        <is>
+          <t>19:48:51</t>
+        </is>
+      </c>
+      <c r="I207" s="10" t="inlineStr"/>
+    </row>
+    <row r="208" ht="22" customHeight="1">
+      <c r="A208" s="9" t="inlineStr">
+        <is>
+          <t>KEY-007</t>
+        </is>
+      </c>
+      <c r="B208" s="10" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C208" s="10" t="inlineStr">
+        <is>
+          <t>Page Up Keyboard Scroll</t>
+        </is>
+      </c>
+      <c r="D208" s="10" t="inlineStr">
+        <is>
+          <t>Send Page Up key press to scroll view</t>
+        </is>
+      </c>
+      <c r="E208" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F208" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G208" s="9" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="H208" s="9" t="inlineStr">
+        <is>
+          <t>19:48:51</t>
+        </is>
+      </c>
+      <c r="I208" s="10" t="inlineStr"/>
+    </row>
+    <row r="209" ht="22" customHeight="1">
+      <c r="A209" s="9" t="inlineStr">
+        <is>
+          <t>KEY-008</t>
+        </is>
+      </c>
+      <c r="B209" s="10" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C209" s="10" t="inlineStr">
+        <is>
+          <t>ARIA Role Landmarks Compliance</t>
+        </is>
+      </c>
+      <c r="D209" s="10" t="inlineStr">
+        <is>
+          <t>Verify navigation and main region ARIA landmark tags</t>
+        </is>
+      </c>
+      <c r="E209" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F209" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G209" s="9" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H209" s="9" t="inlineStr">
+        <is>
+          <t>19:48:51</t>
+        </is>
+      </c>
+      <c r="I209" s="10" t="inlineStr"/>
+    </row>
+    <row r="210" ht="22" customHeight="1">
+      <c r="A210" s="9" t="inlineStr">
+        <is>
+          <t>KEY-009</t>
+        </is>
+      </c>
+      <c r="B210" s="10" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C210" s="10" t="inlineStr">
+        <is>
+          <t>Image Alt Tag Attributes Verification</t>
+        </is>
+      </c>
+      <c r="D210" s="10" t="inlineStr">
+        <is>
+          <t>Ensure images contain descriptive alt text attributes</t>
+        </is>
+      </c>
+      <c r="E210" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F210" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G210" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" s="9" t="inlineStr">
+        <is>
+          <t>19:48:51</t>
+        </is>
+      </c>
+      <c r="I210" s="10" t="inlineStr"/>
+    </row>
+    <row r="211" ht="22" customHeight="1">
+      <c r="A211" s="9" t="inlineStr">
+        <is>
+          <t>KEY-010</t>
+        </is>
+      </c>
+      <c r="B211" s="10" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C211" s="10" t="inlineStr">
+        <is>
+          <t>Color Contrast Ratio Compliance Check</t>
+        </is>
+      </c>
+      <c r="D211" s="10" t="inlineStr">
+        <is>
+          <t>Verify legible text foreground to background contrast</t>
+        </is>
+      </c>
+      <c r="E211" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F211" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G211" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" s="9" t="inlineStr">
+        <is>
+          <t>19:48:51</t>
+        </is>
+      </c>
+      <c r="I211" s="10" t="inlineStr"/>
+    </row>
+    <row r="212" ht="22" customHeight="1">
+      <c r="A212" s="9" t="inlineStr">
+        <is>
+          <t>KEY-011</t>
+        </is>
+      </c>
+      <c r="B212" s="10" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C212" s="10" t="inlineStr">
+        <is>
+          <t>Screen Reader Form Input Labels Check</t>
+        </is>
+      </c>
+      <c r="D212" s="10" t="inlineStr">
+        <is>
+          <t>Ensure form fields have associated label tags</t>
+        </is>
+      </c>
+      <c r="E212" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F212" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G212" s="9" t="n">
+        <v>3.018</v>
+      </c>
+      <c r="H212" s="9" t="inlineStr">
+        <is>
+          <t>19:48:51</t>
+        </is>
+      </c>
+      <c r="I212" s="10" t="inlineStr"/>
+    </row>
+    <row r="213" ht="22" customHeight="1">
+      <c r="A213" s="9" t="inlineStr">
+        <is>
+          <t>KEY-012</t>
+        </is>
+      </c>
+      <c r="B213" s="10" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C213" s="10" t="inlineStr">
+        <is>
+          <t>Focus Trap in Active Modal Dialogs</t>
+        </is>
+      </c>
+      <c r="D213" s="10" t="inlineStr">
+        <is>
+          <t>Verify focus stays inside modal overlay when open</t>
+        </is>
+      </c>
+      <c r="E213" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F213" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G213" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" s="9" t="inlineStr">
+        <is>
+          <t>19:48:54</t>
+        </is>
+      </c>
+      <c r="I213" s="10" t="inlineStr"/>
+    </row>
+    <row r="214" ht="22" customHeight="1">
+      <c r="A214" s="9" t="inlineStr">
+        <is>
+          <t>EXP-001</t>
+        </is>
+      </c>
+      <c r="B214" s="10" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C214" s="10" t="inlineStr">
+        <is>
+          <t>Verify LocalStorage State Persistence</t>
+        </is>
+      </c>
+      <c r="D214" s="10" t="inlineStr">
+        <is>
+          <t>Verify browser LocalStorage holds active user session</t>
+        </is>
+      </c>
+      <c r="E214" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F214" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G214" s="9" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H214" s="9" t="inlineStr">
+        <is>
+          <t>19:48:54</t>
+        </is>
+      </c>
+      <c r="I214" s="10" t="inlineStr"/>
+    </row>
+    <row r="215" ht="22" customHeight="1">
+      <c r="A215" s="9" t="inlineStr">
+        <is>
+          <t>EXP-002</t>
+        </is>
+      </c>
+      <c r="B215" s="10" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C215" s="10" t="inlineStr">
+        <is>
+          <t>Verify IndexedDB Clinical Storage Record Count</t>
+        </is>
+      </c>
+      <c r="D215" s="10" t="inlineStr">
+        <is>
+          <t>Verify browser IndexedDB database status</t>
+        </is>
+      </c>
+      <c r="E215" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F215" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G215" s="9" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H215" s="9" t="inlineStr">
+        <is>
+          <t>19:48:54</t>
+        </is>
+      </c>
+      <c r="I215" s="10" t="inlineStr"/>
+    </row>
+    <row r="216" ht="22" customHeight="1">
+      <c r="A216" s="9" t="inlineStr">
+        <is>
+          <t>EXP-003</t>
+        </is>
+      </c>
+      <c r="B216" s="10" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C216" s="10" t="inlineStr">
+        <is>
+          <t>Export Full Clinic Database Backup JSON</t>
+        </is>
+      </c>
+      <c r="D216" s="10" t="inlineStr">
+        <is>
+          <t>Trigger full JSON database export action</t>
+        </is>
+      </c>
+      <c r="E216" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F216" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G216" s="9" t="n">
+        <v>6.106</v>
+      </c>
+      <c r="H216" s="9" t="inlineStr">
+        <is>
+          <t>19:48:54</t>
+        </is>
+      </c>
+      <c r="I216" s="10" t="inlineStr"/>
+    </row>
+    <row r="217" ht="22" customHeight="1">
+      <c r="A217" s="9" t="inlineStr">
+        <is>
+          <t>EXP-004</t>
+        </is>
+      </c>
+      <c r="B217" s="10" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C217" s="10" t="inlineStr">
+        <is>
+          <t>Data Backup Timestamp Validation</t>
+        </is>
+      </c>
+      <c r="D217" s="10" t="inlineStr">
+        <is>
+          <t>Verify generated backup file contains current date stamp</t>
+        </is>
+      </c>
+      <c r="E217" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F217" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G217" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" s="9" t="inlineStr">
+        <is>
+          <t>19:49:00</t>
+        </is>
+      </c>
+      <c r="I217" s="10" t="inlineStr"/>
+    </row>
+    <row r="218" ht="22" customHeight="1">
+      <c r="A218" s="9" t="inlineStr">
+        <is>
+          <t>EXP-005</t>
+        </is>
+      </c>
+      <c r="B218" s="10" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C218" s="10" t="inlineStr">
+        <is>
+          <t>Excel Report Generation Engine Trigger</t>
+        </is>
+      </c>
+      <c r="D218" s="10" t="inlineStr">
+        <is>
+          <t>Verify openpyxl report builder setup</t>
+        </is>
+      </c>
+      <c r="E218" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F218" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G218" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" s="9" t="inlineStr">
+        <is>
+          <t>19:49:00</t>
+        </is>
+      </c>
+      <c r="I218" s="10" t="inlineStr"/>
+    </row>
+    <row r="219" ht="22" customHeight="1">
+      <c r="A219" s="9" t="inlineStr">
+        <is>
+          <t>EXP-006</t>
+        </is>
+      </c>
+      <c r="B219" s="10" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C219" s="10" t="inlineStr">
+        <is>
+          <t>Summary Worksheet Row Count Calculation</t>
+        </is>
+      </c>
+      <c r="D219" s="10" t="inlineStr">
+        <is>
+          <t>Verify category breakdown calculation for report</t>
+        </is>
+      </c>
+      <c r="E219" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F219" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G219" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" s="9" t="inlineStr">
+        <is>
+          <t>19:49:00</t>
+        </is>
+      </c>
+      <c r="I219" s="10" t="inlineStr"/>
+    </row>
+    <row r="220" ht="22" customHeight="1">
+      <c r="A220" s="9" t="inlineStr">
+        <is>
+          <t>EXP-007</t>
+        </is>
+      </c>
+      <c r="B220" s="10" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C220" s="10" t="inlineStr">
+        <is>
+          <t>Detailed Test Cases Worksheet Row Count</t>
+        </is>
+      </c>
+      <c r="D220" s="10" t="inlineStr">
+        <is>
+          <t>Verify 218 test case entries format in report</t>
+        </is>
+      </c>
+      <c r="E220" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F220" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G220" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" s="9" t="inlineStr">
+        <is>
+          <t>19:49:00</t>
+        </is>
+      </c>
+      <c r="I220" s="10" t="inlineStr"/>
+    </row>
+    <row r="221" ht="22" customHeight="1">
+      <c r="A221" s="9" t="inlineStr">
+        <is>
+          <t>EXP-008</t>
+        </is>
+      </c>
+      <c r="B221" s="10" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C221" s="10" t="inlineStr">
+        <is>
+          <t>Status Badge Color Fill Formatting Check</t>
+        </is>
+      </c>
+      <c r="D221" s="10" t="inlineStr">
+        <is>
+          <t>Verify green PASS and red FAIL cell fills</t>
+        </is>
+      </c>
+      <c r="E221" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F221" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G221" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" s="9" t="inlineStr">
+        <is>
+          <t>19:49:00</t>
+        </is>
+      </c>
+      <c r="I221" s="10" t="inlineStr"/>
+    </row>
+    <row r="222" ht="22" customHeight="1">
+      <c r="A222" s="9" t="inlineStr">
+        <is>
+          <t>EXP-009</t>
+        </is>
+      </c>
+      <c r="B222" s="10" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C222" s="10" t="inlineStr">
+        <is>
+          <t>Column Auto-fit Width Calculation Check</t>
+        </is>
+      </c>
+      <c r="D222" s="10" t="inlineStr">
+        <is>
+          <t>Verify auto-fit column dimensions calculation</t>
+        </is>
+      </c>
+      <c r="E222" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F222" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G222" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" s="9" t="inlineStr">
+        <is>
+          <t>19:49:00</t>
+        </is>
+      </c>
+      <c r="I222" s="10" t="inlineStr"/>
+    </row>
+    <row r="223" ht="22" customHeight="1">
+      <c r="A223" s="9" t="inlineStr">
+        <is>
+          <t>EXP-010</t>
+        </is>
+      </c>
+      <c r="B223" s="10" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C223" s="10" t="inlineStr">
+        <is>
+          <t>Clean Teardown &amp; Log Closure</t>
+        </is>
+      </c>
+      <c r="D223" s="10" t="inlineStr">
+        <is>
+          <t>Complete final assertion and close test suite execution</t>
+        </is>
+      </c>
+      <c r="E223" s="9" t="inlineStr">
+        <is>
+          <t>Live Chrome</t>
+        </is>
+      </c>
+      <c r="F223" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G223" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" s="9" t="inlineStr">
+        <is>
+          <t>19:49:00</t>
+        </is>
+      </c>
+      <c r="I223" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/EndoPredict_Selenium_Test_Report.xlsx
+++ b/EndoPredict_Selenium_Test_Report.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>10.54 sec</t>
+          <t>10.69 sec</t>
         </is>
       </c>
     </row>
@@ -1057,11 +1057,11 @@
         </is>
       </c>
       <c r="G2" s="9" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>13:40:47</t>
+          <t>13:25:05</t>
         </is>
       </c>
       <c r="I2" s="10" t="inlineStr"/>
@@ -1098,11 +1098,11 @@
         </is>
       </c>
       <c r="G3" s="9" t="n">
-        <v>0.255</v>
+        <v>0.257</v>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>13:40:47</t>
+          <t>13:25:05</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr"/>
@@ -1139,11 +1139,11 @@
         </is>
       </c>
       <c r="G4" s="9" t="n">
-        <v>0.251</v>
+        <v>0.233</v>
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>13:40:47</t>
+          <t>13:25:05</t>
         </is>
       </c>
       <c r="I4" s="10" t="inlineStr"/>
@@ -1180,11 +1180,11 @@
         </is>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.258</v>
+        <v>0.305</v>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>13:40:48</t>
+          <t>13:25:05</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr"/>
@@ -1221,11 +1221,11 @@
         </is>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.266</v>
+        <v>0.282</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>13:40:48</t>
+          <t>13:25:06</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
@@ -1262,11 +1262,11 @@
         </is>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.251</v>
+        <v>0.393</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>13:40:48</t>
+          <t>13:25:06</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr"/>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.256</v>
+        <v>0.239</v>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>13:40:48</t>
+          <t>13:25:06</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr"/>
@@ -1344,11 +1344,11 @@
         </is>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.25</v>
+        <v>0.242</v>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>13:40:49</t>
+          <t>13:25:06</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr"/>
@@ -1385,11 +1385,11 @@
         </is>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.267</v>
+        <v>0.259</v>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>13:40:49</t>
+          <t>13:25:07</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
@@ -1426,11 +1426,11 @@
         </is>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.254</v>
+        <v>0.243</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>13:40:49</t>
+          <t>13:25:07</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr"/>
@@ -1467,11 +1467,11 @@
         </is>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.232</v>
+        <v>0.23</v>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>13:40:49</t>
+          <t>13:25:07</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr"/>
@@ -1508,11 +1508,11 @@
         </is>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.218</v>
+        <v>0.217</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>13:40:50</t>
+          <t>13:25:07</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr"/>
@@ -1549,11 +1549,11 @@
         </is>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.223</v>
+        <v>0.222</v>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>13:40:50</t>
+          <t>13:25:08</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr"/>
@@ -1590,11 +1590,11 @@
         </is>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.226</v>
+        <v>0.22</v>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>13:40:50</t>
+          <t>13:25:08</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr"/>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.225</v>
+        <v>0.221</v>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>13:40:50</t>
+          <t>13:25:08</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr"/>
@@ -1672,11 +1672,11 @@
         </is>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.218</v>
+        <v>0.221</v>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>13:40:50</t>
+          <t>13:25:08</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr"/>
@@ -1713,11 +1713,11 @@
         </is>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.226</v>
+        <v>0.222</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>13:40:51</t>
+          <t>13:25:09</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr"/>
@@ -1754,11 +1754,11 @@
         </is>
       </c>
       <c r="G19" s="9" t="n">
-        <v>0.226</v>
+        <v>0.211</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>13:40:51</t>
+          <t>13:25:09</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr"/>
@@ -1795,11 +1795,11 @@
         </is>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.226</v>
+        <v>0.213</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>13:40:51</t>
+          <t>13:25:09</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr"/>
@@ -1836,11 +1836,11 @@
         </is>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.224</v>
+        <v>0.213</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>13:40:51</t>
+          <t>13:25:09</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr"/>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr"/>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr"/>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr"/>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr"/>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr"/>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr"/>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr"/>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr"/>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr"/>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr"/>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr"/>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr"/>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr"/>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr"/>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr"/>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr"/>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr"/>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr"/>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr"/>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr"/>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr"/>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr"/>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr"/>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr"/>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr"/>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr"/>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr"/>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr"/>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr"/>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr"/>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr"/>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr"/>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr"/>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr"/>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr"/>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr"/>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr"/>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr"/>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr"/>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr"/>
@@ -3845,11 +3845,11 @@
         </is>
       </c>
       <c r="G70" s="9" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr"/>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="H71" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr"/>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr"/>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr"/>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr"/>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr"/>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr"/>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr"/>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="H78" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr"/>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="H79" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr"/>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="H80" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr"/>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="H81" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr"/>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="H82" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr"/>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H83" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr"/>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="H84" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr"/>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="H85" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr"/>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="H86" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr"/>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="H87" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr"/>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="H88" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr"/>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="H89" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr"/>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="H90" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr"/>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
-          <t>13:40:52</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr"/>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="H92" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr"/>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="H93" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr"/>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="H94" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr"/>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="H95" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr"/>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="H96" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I96" s="10" t="inlineStr"/>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="H97" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I97" s="10" t="inlineStr"/>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="H98" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I98" s="10" t="inlineStr"/>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="H99" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I99" s="10" t="inlineStr"/>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="H100" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I100" s="10" t="inlineStr"/>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="H101" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I101" s="10" t="inlineStr"/>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="H102" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I102" s="10" t="inlineStr"/>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="H103" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I103" s="10" t="inlineStr"/>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="H104" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I104" s="10" t="inlineStr"/>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="H105" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I105" s="10" t="inlineStr"/>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="H106" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I106" s="10" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I107" s="10" t="inlineStr"/>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="H108" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I108" s="10" t="inlineStr"/>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I109" s="10" t="inlineStr"/>
@@ -5489,7 +5489,7 @@
       </c>
       <c r="H110" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I110" s="10" t="inlineStr"/>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="H111" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I111" s="10" t="inlineStr"/>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="H112" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I112" s="10" t="inlineStr"/>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H113" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I113" s="10" t="inlineStr"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="H114" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I114" s="10" t="inlineStr"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="H115" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I115" s="10" t="inlineStr"/>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="H116" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:10</t>
         </is>
       </c>
       <c r="I116" s="10" t="inlineStr"/>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="H117" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I117" s="10" t="inlineStr"/>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="H118" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I118" s="10" t="inlineStr"/>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="H119" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr"/>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H120" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr"/>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="H121" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr"/>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="H122" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr"/>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="H123" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr"/>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="H124" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr"/>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="H125" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr"/>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="H126" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I126" s="10" t="inlineStr"/>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="H127" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr"/>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="H128" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I128" s="10" t="inlineStr"/>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="H129" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr"/>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="H130" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I130" s="10" t="inlineStr"/>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="H131" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr"/>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="H132" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I132" s="10" t="inlineStr"/>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="H133" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I133" s="10" t="inlineStr"/>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="H134" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I134" s="10" t="inlineStr"/>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="H135" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr"/>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="H136" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I136" s="10" t="inlineStr"/>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="H137" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I137" s="10" t="inlineStr"/>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="H138" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I138" s="10" t="inlineStr"/>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="H139" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr"/>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="H140" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I140" s="10" t="inlineStr"/>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="H141" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr"/>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="H142" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I142" s="10" t="inlineStr"/>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="H143" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr"/>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="H144" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I144" s="10" t="inlineStr"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="H145" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I145" s="10" t="inlineStr"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="H146" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I146" s="10" t="inlineStr"/>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="H147" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I147" s="10" t="inlineStr"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="H148" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I148" s="10" t="inlineStr"/>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="H149" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I149" s="10" t="inlineStr"/>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="H150" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I150" s="10" t="inlineStr"/>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="H151" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I151" s="10" t="inlineStr"/>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="H152" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I152" s="10" t="inlineStr"/>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="H153" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr"/>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="H154" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I154" s="10" t="inlineStr"/>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="H155" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I155" s="10" t="inlineStr"/>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="H156" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I156" s="10" t="inlineStr"/>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="H157" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr"/>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="H158" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I158" s="10" t="inlineStr"/>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="H159" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I159" s="10" t="inlineStr"/>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="H160" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I160" s="10" t="inlineStr"/>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="H161" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I161" s="10" t="inlineStr"/>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="H162" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I162" s="10" t="inlineStr"/>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="H163" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr"/>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="H164" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I164" s="10" t="inlineStr"/>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="H165" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I165" s="10" t="inlineStr"/>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="H166" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I166" s="10" t="inlineStr"/>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="H167" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I167" s="10" t="inlineStr"/>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="H168" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I168" s="10" t="inlineStr"/>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="H169" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I169" s="10" t="inlineStr"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="H170" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I170" s="10" t="inlineStr"/>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="H171" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I171" s="10" t="inlineStr"/>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="H172" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I172" s="10" t="inlineStr"/>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="H173" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I173" s="10" t="inlineStr"/>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H174" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I174" s="10" t="inlineStr"/>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="H175" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I175" s="10" t="inlineStr"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="H176" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I176" s="10" t="inlineStr"/>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="H177" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I177" s="10" t="inlineStr"/>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="H178" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I178" s="10" t="inlineStr"/>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="H179" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I179" s="10" t="inlineStr"/>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="H180" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I180" s="10" t="inlineStr"/>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="H181" s="9" t="inlineStr">
         <is>
-          <t>13:40:53</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I181" s="10" t="inlineStr"/>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="H182" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I182" s="10" t="inlineStr"/>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="H183" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I183" s="10" t="inlineStr"/>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="H184" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I184" s="10" t="inlineStr"/>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="H185" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I185" s="10" t="inlineStr"/>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="H186" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I186" s="10" t="inlineStr"/>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="H187" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I187" s="10" t="inlineStr"/>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="H188" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I188" s="10" t="inlineStr"/>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="H189" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I189" s="10" t="inlineStr"/>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="H190" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I190" s="10" t="inlineStr"/>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="H191" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I191" s="10" t="inlineStr"/>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="H192" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I192" s="10" t="inlineStr"/>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="H193" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I193" s="10" t="inlineStr"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="H194" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I194" s="10" t="inlineStr"/>
@@ -8974,7 +8974,7 @@
       </c>
       <c r="H195" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I195" s="10" t="inlineStr"/>
@@ -9015,7 +9015,7 @@
       </c>
       <c r="H196" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I196" s="10" t="inlineStr"/>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="H197" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I197" s="10" t="inlineStr"/>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="H198" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I198" s="10" t="inlineStr"/>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="H199" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I199" s="10" t="inlineStr"/>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="H200" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I200" s="10" t="inlineStr"/>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="H201" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:11</t>
         </is>
       </c>
       <c r="I201" s="10" t="inlineStr"/>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="H202" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I202" s="10" t="inlineStr"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="H203" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I203" s="10" t="inlineStr"/>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="H204" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I204" s="10" t="inlineStr"/>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="H205" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I205" s="10" t="inlineStr"/>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="H206" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I206" s="10" t="inlineStr"/>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="H207" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I207" s="10" t="inlineStr"/>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="H208" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I208" s="10" t="inlineStr"/>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="H209" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I209" s="10" t="inlineStr"/>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="H210" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I210" s="10" t="inlineStr"/>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="H211" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I211" s="10" t="inlineStr"/>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="H212" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I212" s="10" t="inlineStr"/>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="H213" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I213" s="10" t="inlineStr"/>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="H214" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I214" s="10" t="inlineStr"/>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="H215" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I215" s="10" t="inlineStr"/>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="H216" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I216" s="10" t="inlineStr"/>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="H217" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I217" s="10" t="inlineStr"/>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="H218" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I218" s="10" t="inlineStr"/>
@@ -9958,7 +9958,7 @@
       </c>
       <c r="H219" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I219" s="10" t="inlineStr"/>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="H220" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I220" s="10" t="inlineStr"/>
@@ -10040,7 +10040,7 @@
       </c>
       <c r="H221" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I221" s="10" t="inlineStr"/>
@@ -10081,7 +10081,7 @@
       </c>
       <c r="H222" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I222" s="10" t="inlineStr"/>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="H223" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I223" s="10" t="inlineStr"/>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="H224" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I224" s="10" t="inlineStr"/>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="H225" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I225" s="10" t="inlineStr"/>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="H226" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I226" s="10" t="inlineStr"/>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="H227" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I227" s="10" t="inlineStr"/>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="H228" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I228" s="10" t="inlineStr"/>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="H229" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I229" s="10" t="inlineStr"/>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="H230" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I230" s="10" t="inlineStr"/>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="H231" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I231" s="10" t="inlineStr"/>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="H232" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I232" s="10" t="inlineStr"/>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="H233" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I233" s="10" t="inlineStr"/>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="H234" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I234" s="10" t="inlineStr"/>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H235" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I235" s="10" t="inlineStr"/>
@@ -10655,7 +10655,7 @@
       </c>
       <c r="H236" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I236" s="10" t="inlineStr"/>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="H237" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I237" s="10" t="inlineStr"/>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="H238" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I238" s="10" t="inlineStr"/>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="H239" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I239" s="10" t="inlineStr"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="H240" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I240" s="10" t="inlineStr"/>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="H241" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I241" s="10" t="inlineStr"/>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="H242" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I242" s="10" t="inlineStr"/>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="H243" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I243" s="10" t="inlineStr"/>
@@ -10983,7 +10983,7 @@
       </c>
       <c r="H244" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I244" s="10" t="inlineStr"/>
@@ -11024,7 +11024,7 @@
       </c>
       <c r="H245" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I245" s="10" t="inlineStr"/>
@@ -11065,7 +11065,7 @@
       </c>
       <c r="H246" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I246" s="10" t="inlineStr"/>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="H247" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I247" s="10" t="inlineStr"/>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="H248" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I248" s="10" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="H249" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I249" s="10" t="inlineStr"/>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="H250" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I250" s="10" t="inlineStr"/>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="H251" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I251" s="10" t="inlineStr"/>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="H252" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I252" s="10" t="inlineStr"/>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="H253" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I253" s="10" t="inlineStr"/>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="H254" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I254" s="10" t="inlineStr"/>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="H255" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I255" s="10" t="inlineStr"/>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="H256" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I256" s="10" t="inlineStr"/>
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H257" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I257" s="10" t="inlineStr"/>
@@ -11557,7 +11557,7 @@
       </c>
       <c r="H258" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I258" s="10" t="inlineStr"/>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="H259" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I259" s="10" t="inlineStr"/>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="H260" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I260" s="10" t="inlineStr"/>
@@ -11680,7 +11680,7 @@
       </c>
       <c r="H261" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I261" s="10" t="inlineStr"/>
@@ -11721,7 +11721,7 @@
       </c>
       <c r="H262" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I262" s="10" t="inlineStr"/>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="H263" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I263" s="10" t="inlineStr"/>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="H264" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I264" s="10" t="inlineStr"/>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="H265" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I265" s="10" t="inlineStr"/>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="H266" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I266" s="10" t="inlineStr"/>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="H267" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I267" s="10" t="inlineStr"/>
@@ -11967,7 +11967,7 @@
       </c>
       <c r="H268" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I268" s="10" t="inlineStr"/>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="H269" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I269" s="10" t="inlineStr"/>
@@ -12049,7 +12049,7 @@
       </c>
       <c r="H270" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I270" s="10" t="inlineStr"/>
@@ -12090,7 +12090,7 @@
       </c>
       <c r="H271" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I271" s="10" t="inlineStr"/>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="H272" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I272" s="10" t="inlineStr"/>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="H273" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I273" s="10" t="inlineStr"/>
@@ -12213,7 +12213,7 @@
       </c>
       <c r="H274" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I274" s="10" t="inlineStr"/>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="H275" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I275" s="10" t="inlineStr"/>
@@ -12295,7 +12295,7 @@
       </c>
       <c r="H276" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I276" s="10" t="inlineStr"/>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="H277" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I277" s="10" t="inlineStr"/>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="H278" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I278" s="10" t="inlineStr"/>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="H279" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I279" s="10" t="inlineStr"/>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="H280" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I280" s="10" t="inlineStr"/>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="H281" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I281" s="10" t="inlineStr"/>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="H282" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I282" s="10" t="inlineStr"/>
@@ -12582,7 +12582,7 @@
       </c>
       <c r="H283" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I283" s="10" t="inlineStr"/>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="H284" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I284" s="10" t="inlineStr"/>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="H285" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I285" s="10" t="inlineStr"/>
@@ -12705,7 +12705,7 @@
       </c>
       <c r="H286" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I286" s="10" t="inlineStr"/>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="H287" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I287" s="10" t="inlineStr"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="H288" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I288" s="10" t="inlineStr"/>
@@ -12828,7 +12828,7 @@
       </c>
       <c r="H289" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I289" s="10" t="inlineStr"/>
@@ -12869,7 +12869,7 @@
       </c>
       <c r="H290" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I290" s="10" t="inlineStr"/>
@@ -12910,7 +12910,7 @@
       </c>
       <c r="H291" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I291" s="10" t="inlineStr"/>
@@ -12951,7 +12951,7 @@
       </c>
       <c r="H292" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I292" s="10" t="inlineStr"/>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="H293" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I293" s="10" t="inlineStr"/>
@@ -13033,7 +13033,7 @@
       </c>
       <c r="H294" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I294" s="10" t="inlineStr"/>
@@ -13074,7 +13074,7 @@
       </c>
       <c r="H295" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I295" s="10" t="inlineStr"/>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H296" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I296" s="10" t="inlineStr"/>
@@ -13156,7 +13156,7 @@
       </c>
       <c r="H297" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I297" s="10" t="inlineStr"/>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="H298" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I298" s="10" t="inlineStr"/>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="H299" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I299" s="10" t="inlineStr"/>
@@ -13279,7 +13279,7 @@
       </c>
       <c r="H300" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I300" s="10" t="inlineStr"/>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="H301" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I301" s="10" t="inlineStr"/>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="H302" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I302" s="10" t="inlineStr"/>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="H303" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I303" s="10" t="inlineStr"/>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="H304" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I304" s="10" t="inlineStr"/>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="H305" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I305" s="10" t="inlineStr"/>
@@ -13525,7 +13525,7 @@
       </c>
       <c r="H306" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I306" s="10" t="inlineStr"/>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="H307" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I307" s="10" t="inlineStr"/>
@@ -13607,7 +13607,7 @@
       </c>
       <c r="H308" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I308" s="10" t="inlineStr"/>
@@ -13648,7 +13648,7 @@
       </c>
       <c r="H309" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I309" s="10" t="inlineStr"/>
@@ -13689,7 +13689,7 @@
       </c>
       <c r="H310" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I310" s="10" t="inlineStr"/>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="H311" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I311" s="10" t="inlineStr"/>
@@ -13771,7 +13771,7 @@
       </c>
       <c r="H312" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I312" s="10" t="inlineStr"/>
@@ -13812,7 +13812,7 @@
       </c>
       <c r="H313" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I313" s="10" t="inlineStr"/>
@@ -13853,7 +13853,7 @@
       </c>
       <c r="H314" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I314" s="10" t="inlineStr"/>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="H315" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I315" s="10" t="inlineStr"/>
@@ -13935,7 +13935,7 @@
       </c>
       <c r="H316" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I316" s="10" t="inlineStr"/>
@@ -13976,7 +13976,7 @@
       </c>
       <c r="H317" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I317" s="10" t="inlineStr"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="H318" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I318" s="10" t="inlineStr"/>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="H319" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I319" s="10" t="inlineStr"/>
@@ -14099,7 +14099,7 @@
       </c>
       <c r="H320" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I320" s="10" t="inlineStr"/>
@@ -14140,7 +14140,7 @@
       </c>
       <c r="H321" s="9" t="inlineStr">
         <is>
-          <t>13:40:54</t>
+          <t>13:25:12</t>
         </is>
       </c>
       <c r="I321" s="10" t="inlineStr"/>
